--- a/7_Allegati/Gantt.xlsx
+++ b/7_Allegati/Gantt.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14EA2EAF-D99F-4DFC-8AE5-5603038E928E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE2329B-685E-486E-AC8D-9A9A04E744DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="415" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1666,119 +1666,7 @@
     <cellStyle name="Valuta [0]" xfId="13" builtinId="7" customBuiltin="1"/>
     <cellStyle name="zTestoNascosto" xfId="3" xr:uid="{26E66EE6-E33F-4D77-BAE4-0FB4F5BBF673}"/>
   </cellStyles>
-  <dxfs count="59">
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="56">
     <dxf>
       <font>
         <color auto="1"/>
@@ -2058,6 +1946,24 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="2" tint="-9.9948118533890809E-2"/>
@@ -2141,6 +2047,44 @@
         </right>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2489,21 +2433,21 @@
   </dxfs>
   <tableStyles count="2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Stile tabella Gantt" pivot="0" count="4" xr9:uid="{4904D139-63E4-4221-B7C9-C6C5B7A50FAF}">
-      <tableStyleElement type="wholeTable" dxfId="58"/>
-      <tableStyleElement type="headerRow" dxfId="57"/>
-      <tableStyleElement type="firstRowStripe" dxfId="56"/>
-      <tableStyleElement type="secondRowStripe" dxfId="55"/>
+      <tableStyleElement type="wholeTable" dxfId="55"/>
+      <tableStyleElement type="headerRow" dxfId="54"/>
+      <tableStyleElement type="firstRowStripe" dxfId="53"/>
+      <tableStyleElement type="secondRowStripe" dxfId="52"/>
     </tableStyle>
     <tableStyle name="ElencoAttività" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="54"/>
-      <tableStyleElement type="headerRow" dxfId="53"/>
-      <tableStyleElement type="totalRow" dxfId="52"/>
-      <tableStyleElement type="firstColumn" dxfId="51"/>
-      <tableStyleElement type="lastColumn" dxfId="50"/>
-      <tableStyleElement type="firstRowStripe" dxfId="49"/>
-      <tableStyleElement type="secondRowStripe" dxfId="48"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="47"/>
-      <tableStyleElement type="secondColumnStripe" dxfId="46"/>
+      <tableStyleElement type="wholeTable" dxfId="51"/>
+      <tableStyleElement type="headerRow" dxfId="50"/>
+      <tableStyleElement type="totalRow" dxfId="49"/>
+      <tableStyleElement type="firstColumn" dxfId="48"/>
+      <tableStyleElement type="lastColumn" dxfId="47"/>
+      <tableStyleElement type="firstRowStripe" dxfId="46"/>
+      <tableStyleElement type="secondRowStripe" dxfId="45"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="44"/>
+      <tableStyleElement type="secondColumnStripe" dxfId="43"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -2678,10 +2622,10 @@
           <xdr:rowOff>57150</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>66</xdr:col>
-          <xdr:colOff>162486</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:col>65</xdr:col>
+          <xdr:colOff>38100</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>238125</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2832,7 +2776,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DD82988E-1813-40AE-BDE7-9F0200A703CB}" name="Attivitàcardine4352" displayName="Attivitàcardine4352" ref="B9:G94" totalsRowShown="0" headerRowDxfId="45" dataDxfId="44">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DD82988E-1813-40AE-BDE7-9F0200A703CB}" name="Attivitàcardine4352" displayName="Attivitàcardine4352" ref="B9:G94" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41">
   <autoFilter ref="B9:G94" xr:uid="{29E5A880-80D5-4B65-B5FB-8FB3913D3D27}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -2842,12 +2786,12 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{619BF8F6-D0F1-41AD-871D-FE0240C45A93}" name="Descrizione attività cardine" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{39BD914E-FB02-4352-846C-6D59624DC0B0}" name="Categoria" dataDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{D274194F-BCA0-44F3-84B2-217254EE241C}" name="Assegnato a" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{8385BC6F-56EE-4363-A106-8DB0A1E4EF5A}" name="Avanzamento" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{02926609-7B93-4B6F-BE96-92EC7A949E4B}" name="Inizio" dataDxfId="39" dataCellStyle="Data"/>
-    <tableColumn id="6" xr3:uid="{8FF9BE8E-04B7-4B39-AC27-D2E534204BC3}" name="Giorni" dataDxfId="38"/>
+    <tableColumn id="1" xr3:uid="{619BF8F6-D0F1-41AD-871D-FE0240C45A93}" name="Descrizione attività cardine" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{39BD914E-FB02-4352-846C-6D59624DC0B0}" name="Categoria" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{D274194F-BCA0-44F3-84B2-217254EE241C}" name="Assegnato a" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{8385BC6F-56EE-4363-A106-8DB0A1E4EF5A}" name="Avanzamento" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{02926609-7B93-4B6F-BE96-92EC7A949E4B}" name="Inizio" dataDxfId="36" dataCellStyle="Data"/>
+    <tableColumn id="6" xr3:uid="{8FF9BE8E-04B7-4B39-AC27-D2E534204BC3}" name="Giorni" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo name="ElencoAttività" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -2859,7 +2803,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0EDB95CA-98FE-4198-8801-690B9B480FDF}" name="Attivitàcardine435" displayName="Attivitàcardine435" ref="B9:G36" totalsRowShown="0" headerRowDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0EDB95CA-98FE-4198-8801-690B9B480FDF}" name="Attivitàcardine435" displayName="Attivitàcardine435" ref="B9:G36" totalsRowShown="0" headerRowDxfId="34">
   <autoFilter ref="B9:G36" xr:uid="{29E5A880-80D5-4B65-B5FB-8FB3913D3D27}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -2869,9 +2813,9 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{6E47A83D-ACD7-4EB6-9B84-5195E813945E}" name="Descrizione attività cardine" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{529EEF64-D037-4ACF-8CA4-0C10FE2D1FBB}" name="Categoria" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{711D01BA-2785-403A-9636-CCC7E2ADA584}" name="Assegnato a" dataDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{6E47A83D-ACD7-4EB6-9B84-5195E813945E}" name="Descrizione attività cardine" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{529EEF64-D037-4ACF-8CA4-0C10FE2D1FBB}" name="Categoria" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{711D01BA-2785-403A-9636-CCC7E2ADA584}" name="Assegnato a" dataDxfId="31"/>
     <tableColumn id="4" xr3:uid="{62B00BEF-16BE-4692-B5E2-F287F680F2C1}" name="Avanzamento"/>
     <tableColumn id="5" xr3:uid="{D6D72902-F68F-4E59-A714-AFFF520C647A}" name="Inizio" dataCellStyle="Data"/>
     <tableColumn id="6" xr3:uid="{93E698DE-286F-49ED-AA20-D0C843671DE8}" name="Giorni"/>
@@ -2886,7 +2830,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{876EA49D-634E-482B-8173-880F7B761E2C}" name="Attivitàcardine43524" displayName="Attivitàcardine43524" ref="B9:G36" totalsRowShown="0" headerRowDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{876EA49D-634E-482B-8173-880F7B761E2C}" name="Attivitàcardine43524" displayName="Attivitàcardine43524" ref="B9:G36" totalsRowShown="0" headerRowDxfId="30">
   <autoFilter ref="B9:G36" xr:uid="{29E5A880-80D5-4B65-B5FB-8FB3913D3D27}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -2896,9 +2840,9 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{0971B905-713A-4980-8BBC-DF959C2E61F9}" name="Descrizione attività cardine" dataDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{4492A0B8-068F-4002-9E8D-E1F5FED367F0}" name="Categoria" dataDxfId="31"/>
-    <tableColumn id="3" xr3:uid="{DF1A764E-7050-4528-B7F9-B6AB99372146}" name="Assegnato a" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{0971B905-713A-4980-8BBC-DF959C2E61F9}" name="Descrizione attività cardine" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{4492A0B8-068F-4002-9E8D-E1F5FED367F0}" name="Categoria" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{DF1A764E-7050-4528-B7F9-B6AB99372146}" name="Assegnato a" dataDxfId="27"/>
     <tableColumn id="4" xr3:uid="{47C54592-75B0-4C70-BBF8-0F40483670E9}" name="Avanzamento"/>
     <tableColumn id="5" xr3:uid="{663FB5E0-7616-4EA5-B56A-FF069E2E07D7}" name="Inizio" dataCellStyle="Data"/>
     <tableColumn id="6" xr3:uid="{3B766962-C06F-4E12-BE91-12AB93439874}" name="Giorni"/>
@@ -5362,7 +5306,7 @@
       </c>
       <c r="F12" s="56">
         <f ca="1">TODAY()</f>
-        <v>46066</v>
+        <v>46087</v>
       </c>
       <c r="G12" s="57"/>
       <c r="H12" s="54"/>
@@ -5829,7 +5773,7 @@
       </c>
       <c r="F13" s="56">
         <f ca="1">TODAY()+5</f>
-        <v>46071</v>
+        <v>46092</v>
       </c>
       <c r="G13" s="57"/>
       <c r="H13" s="54"/>
@@ -6296,7 +6240,7 @@
       </c>
       <c r="F14" s="56">
         <f ca="1">F12-3</f>
-        <v>46063</v>
+        <v>46084</v>
       </c>
       <c r="G14" s="57">
         <v>0</v>
@@ -6765,7 +6709,7 @@
       </c>
       <c r="F15" s="56">
         <f ca="1">F12+20</f>
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="G15" s="57">
         <v>0</v>
@@ -7234,7 +7178,7 @@
       </c>
       <c r="F16" s="56">
         <f ca="1">F12+6</f>
-        <v>46072</v>
+        <v>46093</v>
       </c>
       <c r="G16" s="57">
         <v>0</v>
@@ -8167,7 +8111,7 @@
       </c>
       <c r="F18" s="56">
         <f ca="1">F12+6</f>
-        <v>46072</v>
+        <v>46093</v>
       </c>
       <c r="G18" s="57">
         <v>0</v>
@@ -8636,7 +8580,7 @@
       </c>
       <c r="F19" s="56">
         <f ca="1">F18+2</f>
-        <v>46074</v>
+        <v>46095</v>
       </c>
       <c r="G19" s="57">
         <v>0</v>
@@ -9105,7 +9049,7 @@
       </c>
       <c r="F20" s="56">
         <f ca="1">F19+5</f>
-        <v>46079</v>
+        <v>46100</v>
       </c>
       <c r="G20" s="57">
         <v>0</v>
@@ -9574,7 +9518,7 @@
       </c>
       <c r="F21" s="56">
         <f ca="1">F20+2</f>
-        <v>46081</v>
+        <v>46102</v>
       </c>
       <c r="G21" s="57">
         <v>0</v>
@@ -10041,7 +9985,7 @@
       </c>
       <c r="F22" s="56">
         <f ca="1">F21+1</f>
-        <v>46082</v>
+        <v>46103</v>
       </c>
       <c r="G22" s="57">
         <v>0</v>
@@ -10974,7 +10918,7 @@
       </c>
       <c r="F24" s="56">
         <f ca="1">F12+15</f>
-        <v>46081</v>
+        <v>46102</v>
       </c>
       <c r="G24" s="57">
         <v>0</v>
@@ -11443,7 +11387,7 @@
       </c>
       <c r="F25" s="56">
         <f ca="1">F24+3</f>
-        <v>46084</v>
+        <v>46105</v>
       </c>
       <c r="G25" s="57">
         <v>0</v>
@@ -11912,7 +11856,7 @@
       </c>
       <c r="F26" s="56">
         <f ca="1">F25+15</f>
-        <v>46099</v>
+        <v>46120</v>
       </c>
       <c r="G26" s="57">
         <v>0</v>
@@ -12381,7 +12325,7 @@
       </c>
       <c r="F27" s="56">
         <f ca="1">F21+22</f>
-        <v>46103</v>
+        <v>46124</v>
       </c>
       <c r="G27" s="57">
         <v>0</v>
@@ -12850,7 +12794,7 @@
       </c>
       <c r="F28" s="56">
         <f ca="1">F16</f>
-        <v>46072</v>
+        <v>46093</v>
       </c>
       <c r="G28" s="57">
         <v>0</v>
@@ -13781,7 +13725,7 @@
       </c>
       <c r="F30" s="56">
         <f ca="1">F27+3</f>
-        <v>46106</v>
+        <v>46127</v>
       </c>
       <c r="G30" s="57">
         <v>0</v>
@@ -14248,7 +14192,7 @@
       </c>
       <c r="F31" s="56">
         <f ca="1">F30+14</f>
-        <v>46120</v>
+        <v>46141</v>
       </c>
       <c r="G31" s="57">
         <v>0</v>
@@ -14717,7 +14661,7 @@
       </c>
       <c r="F32" s="56">
         <f ca="1">F31+42</f>
-        <v>46162</v>
+        <v>46183</v>
       </c>
       <c r="G32" s="57">
         <v>0</v>
@@ -23049,7 +22993,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="24" t="str">
-        <f t="shared" ref="I50:X94" ca="1" si="92">IF(AND($C50="Obiettivo",I$7&gt;=$F50,I$7&lt;=$F50+$G50-1),2,IF(AND($C50="Attività cardine",I$7&gt;=$F50,I$7&lt;=$F50+$G50-1),1,""))</f>
+        <f t="shared" ref="I50:X93" ca="1" si="92">IF(AND($C50="Obiettivo",I$7&gt;=$F50,I$7&lt;=$F50+$G50-1),2,IF(AND($C50="Attività cardine",I$7&gt;=$F50,I$7&lt;=$F50+$G50-1),1,""))</f>
         <v/>
       </c>
       <c r="J50" s="24" t="str">
@@ -23213,7 +23157,7 @@
         <v/>
       </c>
       <c r="AX50" s="24" t="str">
-        <f t="shared" ref="AX50:BL94" ca="1" si="94">IF(AND($C50="Obiettivo",AX$7&gt;=$F50,AX$7&lt;=$F50+$G50-1),2,IF(AND($C50="Attività cardine",AX$7&gt;=$F50,AX$7&lt;=$F50+$G50-1),1,""))</f>
+        <f t="shared" ref="AX50:BL66" ca="1" si="94">IF(AND($C50="Obiettivo",AX$7&gt;=$F50,AX$7&lt;=$F50+$G50-1),2,IF(AND($C50="Attività cardine",AX$7&gt;=$F50,AX$7&lt;=$F50+$G50-1),1,""))</f>
         <v/>
       </c>
       <c r="AY50" s="24" t="str">
@@ -31067,7 +31011,7 @@
         <v/>
       </c>
       <c r="AX67" s="24" t="str">
-        <f t="shared" ref="AX67:BL94" ca="1" si="101">IF(AND($C67="Obiettivo",AX$7&gt;=$F67,AX$7&lt;=$F67+$G67-1),2,IF(AND($C67="Attività cardine",AX$7&gt;=$F67,AX$7&lt;=$F67+$G67-1),1,""))</f>
+        <f t="shared" ref="AX67:BL83" ca="1" si="101">IF(AND($C67="Obiettivo",AX$7&gt;=$F67,AX$7&lt;=$F67+$G67-1),2,IF(AND($C67="Attività cardine",AX$7&gt;=$F67,AX$7&lt;=$F67+$G67-1),1,""))</f>
         <v/>
       </c>
       <c r="AY67" s="24" t="str">
@@ -38921,7 +38865,7 @@
         <v/>
       </c>
       <c r="AX84" s="24" t="str">
-        <f t="shared" ref="AX84:BM94" ca="1" si="109">IF(AND($C84="Obiettivo",AX$7&gt;=$F84,AX$7&lt;=$F84+$G84-1),2,IF(AND($C84="Attività cardine",AX$7&gt;=$F84,AX$7&lt;=$F84+$G84-1),1,""))</f>
+        <f t="shared" ref="AX84:BM93" ca="1" si="109">IF(AND($C84="Obiettivo",AX$7&gt;=$F84,AX$7&lt;=$F84+$G84-1),2,IF(AND($C84="Attività cardine",AX$7&gt;=$F84,AX$7&lt;=$F84+$G84-1),1,""))</f>
         <v/>
       </c>
       <c r="AY84" s="24" t="str">
@@ -42411,7 +42355,7 @@
         <v/>
       </c>
       <c r="DJ91" s="24" t="str">
-        <f t="shared" ref="DI91:DP94" ca="1" si="113">IF(AND($C91="Obiettivo",DJ$7&gt;=$F91,DJ$7&lt;=$F91+$G91-1),2,IF(AND($C91="Attività cardine",DJ$7&gt;=$F91,DJ$7&lt;=$F91+$G91-1),1,""))</f>
+        <f t="shared" ref="DI91:DP93" ca="1" si="113">IF(AND($C91="Obiettivo",DJ$7&gt;=$F91,DJ$7&lt;=$F91+$G91-1),2,IF(AND($C91="Attività cardine",DJ$7&gt;=$F91,DJ$7&lt;=$F91+$G91-1),1,""))</f>
         <v/>
       </c>
       <c r="DK91" s="24" t="str">
@@ -43516,39 +43460,39 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:AM6 BM6:CQ6 DE6:DP6">
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="26" priority="4">
       <formula>I$7&lt;=EOMONTH($I$7,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:DP6">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="25" priority="2">
       <formula>AND(I$7&lt;=EOMONTH($I$7,1),I$7&gt;EOMONTH($I$7,0))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7:DP94">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>AND(TODAY()&gt;=I$7,TODAY()&lt;J$7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:DP94">
-    <cfRule type="expression" dxfId="28" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="7" stopIfTrue="1">
       <formula>AND($C10="Rischio basso",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="8" stopIfTrue="1">
       <formula>AND($C10="Rischio alto",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="9" stopIfTrue="1">
       <formula>AND($C10="In linea",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="10" stopIfTrue="1">
       <formula>AND($C10="Rischio medio",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="11" stopIfTrue="1">
       <formula>AND(LEN($C10)=0,I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:DP6">
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="18" priority="3">
       <formula>AND(J$7&lt;=EOMONTH($I$7,2),J$7&gt;EOMONTH($I$7,0),J$7&gt;EOMONTH($I$7,1))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43973,7 +43917,7 @@
       </c>
       <c r="C6" s="32" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">IFERROR(IF(MIN(Attivitàcardine435[Inizio])=0,TODAY(),B11(Attivitàcardine435[Inizio])),TODAY())</f>
-        <v>46066</v>
+        <v>46087</v>
       </c>
       <c r="D6" s="48"/>
       <c r="E6" s="30"/>
@@ -43982,7 +43926,7 @@
       <c r="H6" s="27"/>
       <c r="I6" s="88" t="str">
         <f ca="1">TEXT(I7,"mmmm")</f>
-        <v>febbraio</v>
+        <v>marzo</v>
       </c>
       <c r="J6" s="88"/>
       <c r="K6" s="88"/>
@@ -44012,7 +43956,7 @@
       <c r="AC6" s="88"/>
       <c r="AD6" s="88" t="str">
         <f ca="1">IF(OR(TEXT(AD7,"mmmm")=W6,TEXT(AD7,"mmmm")=P6,TEXT(AD7,"mmmm")=I6),"",TEXT(AD7,"mmmm"))</f>
-        <v>marzo</v>
+        <v/>
       </c>
       <c r="AE6" s="88"/>
       <c r="AF6" s="88"/>
@@ -44022,7 +43966,7 @@
       <c r="AJ6" s="88"/>
       <c r="AK6" s="88" t="str">
         <f ca="1">IF(OR(TEXT(AK7,"mmmm")=AD6,TEXT(AK7,"mmmm")=W6,TEXT(AK7,"mmmm")=P6,TEXT(AK7,"mmmm")=I6),"",TEXT(AK7,"mmmm"))</f>
-        <v/>
+        <v>aprile</v>
       </c>
       <c r="AL6" s="88"/>
       <c r="AM6" s="88"/>
@@ -44052,7 +43996,7 @@
       <c r="BE6" s="59"/>
       <c r="BF6" s="59" t="str">
         <f ca="1">IF(OR(TEXT(BF7,"mmmm")=AY6,TEXT(BF7,"mmmm")=AR6,TEXT(BF7,"mmmm")=AK6,TEXT(BF7,"mmmm")=AD6),"",TEXT(BF7,"mmmm"))</f>
-        <v>aprile</v>
+        <v/>
       </c>
       <c r="BG6" s="59"/>
       <c r="BH6" s="59"/>
@@ -44077,227 +44021,227 @@
       <c r="H7" s="27"/>
       <c r="I7" s="117">
         <f ca="1">IFERROR(Inzio_Progetto+Incremento_Scorrimento,TODAY())</f>
-        <v>46067</v>
+        <v>46088</v>
       </c>
       <c r="J7" s="118">
         <f ca="1">I7+1</f>
-        <v>46068</v>
+        <v>46089</v>
       </c>
       <c r="K7" s="118">
         <f t="shared" ref="K7:AX7" ca="1" si="0">J7+1</f>
-        <v>46069</v>
+        <v>46090</v>
       </c>
       <c r="L7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46070</v>
+        <v>46091</v>
       </c>
       <c r="M7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46071</v>
+        <v>46092</v>
       </c>
       <c r="N7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46072</v>
+        <v>46093</v>
       </c>
       <c r="O7" s="119">
         <f t="shared" ca="1" si="0"/>
-        <v>46073</v>
+        <v>46094</v>
       </c>
       <c r="P7" s="118">
         <f ca="1">O7+1</f>
-        <v>46074</v>
+        <v>46095</v>
       </c>
       <c r="Q7" s="118">
         <f ca="1">P7+1</f>
-        <v>46075</v>
+        <v>46096</v>
       </c>
       <c r="R7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46076</v>
+        <v>46097</v>
       </c>
       <c r="S7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46077</v>
+        <v>46098</v>
       </c>
       <c r="T7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46078</v>
+        <v>46099</v>
       </c>
       <c r="U7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46079</v>
+        <v>46100</v>
       </c>
       <c r="V7" s="119">
         <f t="shared" ca="1" si="0"/>
-        <v>46080</v>
+        <v>46101</v>
       </c>
       <c r="W7" s="118">
         <f ca="1">V7+1</f>
-        <v>46081</v>
+        <v>46102</v>
       </c>
       <c r="X7" s="118">
         <f ca="1">W7+1</f>
-        <v>46082</v>
+        <v>46103</v>
       </c>
       <c r="Y7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46083</v>
+        <v>46104</v>
       </c>
       <c r="Z7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46084</v>
+        <v>46105</v>
       </c>
       <c r="AA7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46085</v>
+        <v>46106</v>
       </c>
       <c r="AB7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="AC7" s="119">
         <f t="shared" ca="1" si="0"/>
-        <v>46087</v>
+        <v>46108</v>
       </c>
       <c r="AD7" s="118">
         <f ca="1">AC7+1</f>
-        <v>46088</v>
+        <v>46109</v>
       </c>
       <c r="AE7" s="118">
         <f ca="1">AD7+1</f>
-        <v>46089</v>
+        <v>46110</v>
       </c>
       <c r="AF7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46090</v>
+        <v>46111</v>
       </c>
       <c r="AG7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46091</v>
+        <v>46112</v>
       </c>
       <c r="AH7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46092</v>
+        <v>46113</v>
       </c>
       <c r="AI7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46093</v>
+        <v>46114</v>
       </c>
       <c r="AJ7" s="119">
         <f t="shared" ca="1" si="0"/>
-        <v>46094</v>
+        <v>46115</v>
       </c>
       <c r="AK7" s="118">
         <f ca="1">AJ7+1</f>
-        <v>46095</v>
+        <v>46116</v>
       </c>
       <c r="AL7" s="118">
         <f ca="1">AK7+1</f>
-        <v>46096</v>
+        <v>46117</v>
       </c>
       <c r="AM7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46097</v>
+        <v>46118</v>
       </c>
       <c r="AN7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46098</v>
+        <v>46119</v>
       </c>
       <c r="AO7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46099</v>
+        <v>46120</v>
       </c>
       <c r="AP7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46100</v>
+        <v>46121</v>
       </c>
       <c r="AQ7" s="119">
         <f t="shared" ca="1" si="0"/>
-        <v>46101</v>
+        <v>46122</v>
       </c>
       <c r="AR7" s="118">
         <f ca="1">AQ7+1</f>
-        <v>46102</v>
+        <v>46123</v>
       </c>
       <c r="AS7" s="118">
         <f ca="1">AR7+1</f>
-        <v>46103</v>
+        <v>46124</v>
       </c>
       <c r="AT7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46104</v>
+        <v>46125</v>
       </c>
       <c r="AU7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46105</v>
+        <v>46126</v>
       </c>
       <c r="AV7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46106</v>
+        <v>46127</v>
       </c>
       <c r="AW7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46107</v>
+        <v>46128</v>
       </c>
       <c r="AX7" s="119">
         <f t="shared" ca="1" si="0"/>
-        <v>46108</v>
+        <v>46129</v>
       </c>
       <c r="AY7" s="118">
         <f ca="1">AX7+1</f>
-        <v>46109</v>
+        <v>46130</v>
       </c>
       <c r="AZ7" s="118">
         <f ca="1">AY7+1</f>
-        <v>46110</v>
+        <v>46131</v>
       </c>
       <c r="BA7" s="118">
         <f t="shared" ref="BA7:BE7" ca="1" si="1">AZ7+1</f>
-        <v>46111</v>
+        <v>46132</v>
       </c>
       <c r="BB7" s="118">
         <f t="shared" ca="1" si="1"/>
-        <v>46112</v>
+        <v>46133</v>
       </c>
       <c r="BC7" s="118">
         <f t="shared" ca="1" si="1"/>
-        <v>46113</v>
+        <v>46134</v>
       </c>
       <c r="BD7" s="118">
         <f t="shared" ca="1" si="1"/>
-        <v>46114</v>
+        <v>46135</v>
       </c>
       <c r="BE7" s="119">
         <f t="shared" ca="1" si="1"/>
-        <v>46115</v>
+        <v>46136</v>
       </c>
       <c r="BF7" s="118">
         <f ca="1">BE7+1</f>
-        <v>46116</v>
+        <v>46137</v>
       </c>
       <c r="BG7" s="118">
         <f ca="1">BF7+1</f>
-        <v>46117</v>
+        <v>46138</v>
       </c>
       <c r="BH7" s="118">
         <f t="shared" ref="BH7:BL7" ca="1" si="2">BG7+1</f>
-        <v>46118</v>
+        <v>46139</v>
       </c>
       <c r="BI7" s="118">
         <f t="shared" ca="1" si="2"/>
-        <v>46119</v>
+        <v>46140</v>
       </c>
       <c r="BJ7" s="118">
         <f t="shared" ca="1" si="2"/>
-        <v>46120</v>
+        <v>46141</v>
       </c>
       <c r="BK7" s="118">
         <f t="shared" ca="1" si="2"/>
-        <v>46121</v>
+        <v>46142</v>
       </c>
       <c r="BL7" s="120">
         <f t="shared" ca="1" si="2"/>
-        <v>46122</v>
+        <v>46143</v>
       </c>
       <c r="BM7" s="30"/>
     </row>
@@ -44937,7 +44881,7 @@
       </c>
       <c r="F12" s="21">
         <f ca="1">TODAY()</f>
-        <v>46066</v>
+        <v>46087</v>
       </c>
       <c r="G12" s="22">
         <v>3</v>
@@ -45181,7 +45125,7 @@
       <c r="E13" s="20"/>
       <c r="F13" s="21">
         <f ca="1">TODAY()+5</f>
-        <v>46071</v>
+        <v>46092</v>
       </c>
       <c r="G13" s="22">
         <v>1</v>
@@ -45427,7 +45371,7 @@
       </c>
       <c r="F14" s="21">
         <f ca="1">F12-3</f>
-        <v>46063</v>
+        <v>46084</v>
       </c>
       <c r="G14" s="22">
         <v>10</v>
@@ -45671,7 +45615,7 @@
       <c r="E15" s="20"/>
       <c r="F15" s="21">
         <f ca="1">F12+20</f>
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="G15" s="22">
         <v>1</v>
@@ -45917,7 +45861,7 @@
       </c>
       <c r="F16" s="21">
         <f ca="1">F12+6</f>
-        <v>46072</v>
+        <v>46093</v>
       </c>
       <c r="G16" s="22">
         <v>6</v>
@@ -46400,7 +46344,7 @@
       </c>
       <c r="F18" s="21">
         <f ca="1">F12+6</f>
-        <v>46072</v>
+        <v>46093</v>
       </c>
       <c r="G18" s="22">
         <v>13</v>
@@ -46646,7 +46590,7 @@
       </c>
       <c r="F19" s="21">
         <f ca="1">F18+2</f>
-        <v>46074</v>
+        <v>46095</v>
       </c>
       <c r="G19" s="22">
         <v>9</v>
@@ -46892,7 +46836,7 @@
       </c>
       <c r="F20" s="21">
         <f ca="1">F19+5</f>
-        <v>46079</v>
+        <v>46100</v>
       </c>
       <c r="G20" s="22">
         <v>11</v>
@@ -47136,7 +47080,7 @@
       <c r="E21" s="20"/>
       <c r="F21" s="21">
         <f ca="1">F20+2</f>
-        <v>46081</v>
+        <v>46102</v>
       </c>
       <c r="G21" s="22">
         <v>1</v>
@@ -47378,7 +47322,7 @@
       <c r="E22" s="20"/>
       <c r="F22" s="21">
         <f ca="1">F21+1</f>
-        <v>46082</v>
+        <v>46103</v>
       </c>
       <c r="G22" s="22">
         <v>24</v>
@@ -47859,7 +47803,7 @@
       <c r="E24" s="20"/>
       <c r="F24" s="21">
         <f ca="1">F12+15</f>
-        <v>46081</v>
+        <v>46102</v>
       </c>
       <c r="G24" s="22">
         <v>4</v>
@@ -48103,7 +48047,7 @@
       <c r="E25" s="20"/>
       <c r="F25" s="21">
         <f ca="1">F24+3</f>
-        <v>46084</v>
+        <v>46105</v>
       </c>
       <c r="G25" s="22">
         <v>14</v>
@@ -48347,7 +48291,7 @@
       <c r="E26" s="20"/>
       <c r="F26" s="21">
         <f ca="1">F25+15</f>
-        <v>46099</v>
+        <v>46120</v>
       </c>
       <c r="G26" s="22">
         <v>6</v>
@@ -48591,7 +48535,7 @@
       <c r="E27" s="20"/>
       <c r="F27" s="21">
         <f ca="1">F21+22</f>
-        <v>46103</v>
+        <v>46124</v>
       </c>
       <c r="G27" s="22">
         <v>3</v>
@@ -48835,7 +48779,7 @@
       <c r="E28" s="20"/>
       <c r="F28" s="21">
         <f ca="1">F16</f>
-        <v>46072</v>
+        <v>46093</v>
       </c>
       <c r="G28" s="22">
         <v>19</v>
@@ -49314,7 +49258,7 @@
       <c r="E30" s="20"/>
       <c r="F30" s="21">
         <f ca="1">F27+3</f>
-        <v>46106</v>
+        <v>46127</v>
       </c>
       <c r="G30" s="22">
         <v>15</v>
@@ -49556,7 +49500,7 @@
       <c r="E31" s="20"/>
       <c r="F31" s="21">
         <f ca="1">F30+14</f>
-        <v>46120</v>
+        <v>46141</v>
       </c>
       <c r="G31" s="22">
         <v>5</v>
@@ -49800,7 +49744,7 @@
       <c r="E32" s="20"/>
       <c r="F32" s="21">
         <f ca="1">F31+42</f>
-        <v>46162</v>
+        <v>46183</v>
       </c>
       <c r="G32" s="22">
         <v>1</v>
@@ -50844,39 +50788,39 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:AM6">
-    <cfRule type="expression" dxfId="23" priority="4">
+    <cfRule type="expression" dxfId="17" priority="4">
       <formula>I$7&lt;=EOMONTH($I$7,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:BL6">
-    <cfRule type="expression" dxfId="22" priority="2">
+    <cfRule type="expression" dxfId="16" priority="2">
       <formula>AND(I$7&lt;=EOMONTH($I$7,1),I$7&gt;EOMONTH($I$7,0))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7:BL36">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>AND(TODAY()&gt;=I$7,TODAY()&lt;J$7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:BL35">
-    <cfRule type="expression" dxfId="20" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="7" stopIfTrue="1">
       <formula>AND($C10="Rischio basso",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="8" stopIfTrue="1">
       <formula>AND($C10="Rischio alto",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="9" stopIfTrue="1">
       <formula>AND($C10="In linea",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="10" stopIfTrue="1">
       <formula>AND($C10="Rischio medio",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="11" stopIfTrue="1">
       <formula>AND(LEN($C10)=0,I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:BL6">
-    <cfRule type="expression" dxfId="15" priority="3">
+    <cfRule type="expression" dxfId="9" priority="3">
       <formula>AND(J$7&lt;=EOMONTH($I$7,2),J$7&gt;EOMONTH($I$7,0),J$7&gt;EOMONTH($I$7,1))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -51177,7 +51121,7 @@
       </c>
       <c r="C6" s="74" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">IFERROR(IF(MIN(Attivitàcardine43524[Inizio])=0,TODAY(),B11(Attivitàcardine43524[Inizio])),TODAY())</f>
-        <v>46066</v>
+        <v>46087</v>
       </c>
       <c r="D6" s="75"/>
       <c r="E6" s="69"/>
@@ -51186,7 +51130,7 @@
       <c r="H6" s="69"/>
       <c r="I6" s="85" t="str">
         <f ca="1">TEXT(I7,"mmmm")</f>
-        <v>febbraio</v>
+        <v>marzo</v>
       </c>
       <c r="J6" s="85"/>
       <c r="K6" s="85"/>
@@ -51216,7 +51160,7 @@
       <c r="AC6" s="85"/>
       <c r="AD6" s="85" t="str">
         <f ca="1">IF(OR(TEXT(AD7,"mmmm")=W6,TEXT(AD7,"mmmm")=P6,TEXT(AD7,"mmmm")=I6),"",TEXT(AD7,"mmmm"))</f>
-        <v>marzo</v>
+        <v/>
       </c>
       <c r="AE6" s="85"/>
       <c r="AF6" s="85"/>
@@ -51226,7 +51170,7 @@
       <c r="AJ6" s="85"/>
       <c r="AK6" s="85" t="str">
         <f ca="1">IF(OR(TEXT(AK7,"mmmm")=AD6,TEXT(AK7,"mmmm")=W6,TEXT(AK7,"mmmm")=P6,TEXT(AK7,"mmmm")=I6),"",TEXT(AK7,"mmmm"))</f>
-        <v/>
+        <v>aprile</v>
       </c>
       <c r="AL6" s="85"/>
       <c r="AM6" s="85"/>
@@ -51256,7 +51200,7 @@
       <c r="BE6" s="84"/>
       <c r="BF6" s="84" t="str">
         <f ca="1">IF(OR(TEXT(BF7,"mmmm")=AY6,TEXT(BF7,"mmmm")=AR6,TEXT(BF7,"mmmm")=AK6,TEXT(BF7,"mmmm")=AD6),"",TEXT(BF7,"mmmm"))</f>
-        <v>aprile</v>
+        <v/>
       </c>
       <c r="BG6" s="84"/>
       <c r="BH6" s="84"/>
@@ -51280,227 +51224,227 @@
       <c r="H7" s="77"/>
       <c r="I7" s="109">
         <f ca="1">IFERROR(Inzio_Progetto+Incremento_Scorrimento,TODAY())</f>
-        <v>46067</v>
+        <v>46088</v>
       </c>
       <c r="J7" s="110">
         <f ca="1">I7+1</f>
-        <v>46068</v>
+        <v>46089</v>
       </c>
       <c r="K7" s="110">
         <f t="shared" ref="K7:AX7" ca="1" si="0">J7+1</f>
-        <v>46069</v>
+        <v>46090</v>
       </c>
       <c r="L7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46070</v>
+        <v>46091</v>
       </c>
       <c r="M7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46071</v>
+        <v>46092</v>
       </c>
       <c r="N7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46072</v>
+        <v>46093</v>
       </c>
       <c r="O7" s="111">
         <f t="shared" ca="1" si="0"/>
-        <v>46073</v>
+        <v>46094</v>
       </c>
       <c r="P7" s="110">
         <f ca="1">O7+1</f>
-        <v>46074</v>
+        <v>46095</v>
       </c>
       <c r="Q7" s="110">
         <f ca="1">P7+1</f>
-        <v>46075</v>
+        <v>46096</v>
       </c>
       <c r="R7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46076</v>
+        <v>46097</v>
       </c>
       <c r="S7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46077</v>
+        <v>46098</v>
       </c>
       <c r="T7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46078</v>
+        <v>46099</v>
       </c>
       <c r="U7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46079</v>
+        <v>46100</v>
       </c>
       <c r="V7" s="111">
         <f t="shared" ca="1" si="0"/>
-        <v>46080</v>
+        <v>46101</v>
       </c>
       <c r="W7" s="110">
         <f ca="1">V7+1</f>
-        <v>46081</v>
+        <v>46102</v>
       </c>
       <c r="X7" s="110">
         <f ca="1">W7+1</f>
-        <v>46082</v>
+        <v>46103</v>
       </c>
       <c r="Y7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46083</v>
+        <v>46104</v>
       </c>
       <c r="Z7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46084</v>
+        <v>46105</v>
       </c>
       <c r="AA7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46085</v>
+        <v>46106</v>
       </c>
       <c r="AB7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="AC7" s="111">
         <f t="shared" ca="1" si="0"/>
-        <v>46087</v>
+        <v>46108</v>
       </c>
       <c r="AD7" s="110">
         <f ca="1">AC7+1</f>
-        <v>46088</v>
+        <v>46109</v>
       </c>
       <c r="AE7" s="110">
         <f ca="1">AD7+1</f>
-        <v>46089</v>
+        <v>46110</v>
       </c>
       <c r="AF7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46090</v>
+        <v>46111</v>
       </c>
       <c r="AG7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46091</v>
+        <v>46112</v>
       </c>
       <c r="AH7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46092</v>
+        <v>46113</v>
       </c>
       <c r="AI7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46093</v>
+        <v>46114</v>
       </c>
       <c r="AJ7" s="111">
         <f t="shared" ca="1" si="0"/>
-        <v>46094</v>
+        <v>46115</v>
       </c>
       <c r="AK7" s="110">
         <f ca="1">AJ7+1</f>
-        <v>46095</v>
+        <v>46116</v>
       </c>
       <c r="AL7" s="110">
         <f ca="1">AK7+1</f>
-        <v>46096</v>
+        <v>46117</v>
       </c>
       <c r="AM7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46097</v>
+        <v>46118</v>
       </c>
       <c r="AN7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46098</v>
+        <v>46119</v>
       </c>
       <c r="AO7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46099</v>
+        <v>46120</v>
       </c>
       <c r="AP7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46100</v>
+        <v>46121</v>
       </c>
       <c r="AQ7" s="111">
         <f t="shared" ca="1" si="0"/>
-        <v>46101</v>
+        <v>46122</v>
       </c>
       <c r="AR7" s="110">
         <f ca="1">AQ7+1</f>
-        <v>46102</v>
+        <v>46123</v>
       </c>
       <c r="AS7" s="110">
         <f ca="1">AR7+1</f>
-        <v>46103</v>
+        <v>46124</v>
       </c>
       <c r="AT7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46104</v>
+        <v>46125</v>
       </c>
       <c r="AU7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46105</v>
+        <v>46126</v>
       </c>
       <c r="AV7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46106</v>
+        <v>46127</v>
       </c>
       <c r="AW7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46107</v>
+        <v>46128</v>
       </c>
       <c r="AX7" s="111">
         <f t="shared" ca="1" si="0"/>
-        <v>46108</v>
+        <v>46129</v>
       </c>
       <c r="AY7" s="110">
         <f ca="1">AX7+1</f>
-        <v>46109</v>
+        <v>46130</v>
       </c>
       <c r="AZ7" s="110">
         <f ca="1">AY7+1</f>
-        <v>46110</v>
+        <v>46131</v>
       </c>
       <c r="BA7" s="110">
         <f t="shared" ref="BA7:BE7" ca="1" si="1">AZ7+1</f>
-        <v>46111</v>
+        <v>46132</v>
       </c>
       <c r="BB7" s="110">
         <f t="shared" ca="1" si="1"/>
-        <v>46112</v>
+        <v>46133</v>
       </c>
       <c r="BC7" s="110">
         <f t="shared" ca="1" si="1"/>
-        <v>46113</v>
+        <v>46134</v>
       </c>
       <c r="BD7" s="110">
         <f t="shared" ca="1" si="1"/>
-        <v>46114</v>
+        <v>46135</v>
       </c>
       <c r="BE7" s="111">
         <f t="shared" ca="1" si="1"/>
-        <v>46115</v>
+        <v>46136</v>
       </c>
       <c r="BF7" s="110">
         <f ca="1">BE7+1</f>
-        <v>46116</v>
+        <v>46137</v>
       </c>
       <c r="BG7" s="110">
         <f ca="1">BF7+1</f>
-        <v>46117</v>
+        <v>46138</v>
       </c>
       <c r="BH7" s="110">
         <f t="shared" ref="BH7:BL7" ca="1" si="2">BG7+1</f>
-        <v>46118</v>
+        <v>46139</v>
       </c>
       <c r="BI7" s="110">
         <f t="shared" ca="1" si="2"/>
-        <v>46119</v>
+        <v>46140</v>
       </c>
       <c r="BJ7" s="110">
         <f t="shared" ca="1" si="2"/>
-        <v>46120</v>
+        <v>46141</v>
       </c>
       <c r="BK7" s="110">
         <f t="shared" ca="1" si="2"/>
-        <v>46121</v>
+        <v>46142</v>
       </c>
       <c r="BL7" s="111">
         <f t="shared" ca="1" si="2"/>
-        <v>46122</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="8" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -52134,7 +52078,7 @@
       </c>
       <c r="F12" s="56">
         <f ca="1">TODAY()</f>
-        <v>46066</v>
+        <v>46087</v>
       </c>
       <c r="G12" s="57">
         <v>3</v>
@@ -52377,7 +52321,7 @@
       <c r="E13" s="55"/>
       <c r="F13" s="56">
         <f ca="1">TODAY()+5</f>
-        <v>46071</v>
+        <v>46092</v>
       </c>
       <c r="G13" s="57">
         <v>1</v>
@@ -52622,7 +52566,7 @@
       </c>
       <c r="F14" s="56">
         <f ca="1">F12-3</f>
-        <v>46063</v>
+        <v>46084</v>
       </c>
       <c r="G14" s="57">
         <v>10</v>
@@ -52865,7 +52809,7 @@
       <c r="E15" s="55"/>
       <c r="F15" s="56">
         <f ca="1">F12+20</f>
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="G15" s="57">
         <v>1</v>
@@ -53110,7 +53054,7 @@
       </c>
       <c r="F16" s="56">
         <f ca="1">F12+6</f>
-        <v>46072</v>
+        <v>46093</v>
       </c>
       <c r="G16" s="57">
         <v>6</v>
@@ -53591,7 +53535,7 @@
       </c>
       <c r="F18" s="56">
         <f ca="1">F12+6</f>
-        <v>46072</v>
+        <v>46093</v>
       </c>
       <c r="G18" s="57">
         <v>13</v>
@@ -53836,7 +53780,7 @@
       </c>
       <c r="F19" s="56">
         <f ca="1">F18+2</f>
-        <v>46074</v>
+        <v>46095</v>
       </c>
       <c r="G19" s="57">
         <v>9</v>
@@ -54081,7 +54025,7 @@
       </c>
       <c r="F20" s="56">
         <f ca="1">F19+5</f>
-        <v>46079</v>
+        <v>46100</v>
       </c>
       <c r="G20" s="57">
         <v>11</v>
@@ -54324,7 +54268,7 @@
       <c r="E21" s="55"/>
       <c r="F21" s="56">
         <f ca="1">F20+2</f>
-        <v>46081</v>
+        <v>46102</v>
       </c>
       <c r="G21" s="57">
         <v>1</v>
@@ -54565,7 +54509,7 @@
       <c r="E22" s="55"/>
       <c r="F22" s="56">
         <f ca="1">F21+1</f>
-        <v>46082</v>
+        <v>46103</v>
       </c>
       <c r="G22" s="57">
         <v>24</v>
@@ -55044,7 +54988,7 @@
       <c r="E24" s="55"/>
       <c r="F24" s="56">
         <f ca="1">F12+15</f>
-        <v>46081</v>
+        <v>46102</v>
       </c>
       <c r="G24" s="57">
         <v>4</v>
@@ -55287,7 +55231,7 @@
       <c r="E25" s="55"/>
       <c r="F25" s="56">
         <f ca="1">F24+3</f>
-        <v>46084</v>
+        <v>46105</v>
       </c>
       <c r="G25" s="57">
         <v>14</v>
@@ -55530,7 +55474,7 @@
       <c r="E26" s="55"/>
       <c r="F26" s="56">
         <f ca="1">F25+15</f>
-        <v>46099</v>
+        <v>46120</v>
       </c>
       <c r="G26" s="57">
         <v>6</v>
@@ -55773,7 +55717,7 @@
       <c r="E27" s="55"/>
       <c r="F27" s="56">
         <f ca="1">F21+22</f>
-        <v>46103</v>
+        <v>46124</v>
       </c>
       <c r="G27" s="57">
         <v>3</v>
@@ -56016,7 +55960,7 @@
       <c r="E28" s="55"/>
       <c r="F28" s="56">
         <f ca="1">F16</f>
-        <v>46072</v>
+        <v>46093</v>
       </c>
       <c r="G28" s="57">
         <v>19</v>
@@ -56493,7 +56437,7 @@
       <c r="E30" s="55"/>
       <c r="F30" s="56">
         <f ca="1">F27+3</f>
-        <v>46106</v>
+        <v>46127</v>
       </c>
       <c r="G30" s="57">
         <v>15</v>
@@ -56734,7 +56678,7 @@
       <c r="E31" s="55"/>
       <c r="F31" s="56">
         <f ca="1">F30+14</f>
-        <v>46120</v>
+        <v>46141</v>
       </c>
       <c r="G31" s="57">
         <v>5</v>
@@ -56977,7 +56921,7 @@
       <c r="E32" s="55"/>
       <c r="F32" s="56">
         <f ca="1">F31+42</f>
-        <v>46162</v>
+        <v>46183</v>
       </c>
       <c r="G32" s="57">
         <v>1</v>
@@ -58017,39 +57961,39 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:AM6">
-    <cfRule type="expression" dxfId="14" priority="4">
+    <cfRule type="expression" dxfId="8" priority="4">
       <formula>I$7&lt;=EOMONTH($I$7,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:BL6">
-    <cfRule type="expression" dxfId="13" priority="2">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>AND(I$7&lt;=EOMONTH($I$7,1),I$7&gt;EOMONTH($I$7,0))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7:BL36">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>AND(TODAY()&gt;=I$7,TODAY()&lt;J$7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:BL35">
-    <cfRule type="expression" dxfId="11" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
       <formula>AND($C10="Rischio basso",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
       <formula>AND($C10="Rischio alto",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="9" stopIfTrue="1">
       <formula>AND($C10="In linea",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="10" stopIfTrue="1">
       <formula>AND($C10="Rischio medio",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="11" stopIfTrue="1">
       <formula>AND(LEN($C10)=0,I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:BL6">
-    <cfRule type="expression" dxfId="6" priority="3">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>AND(J$7&lt;=EOMONTH($I$7,2),J$7&gt;EOMONTH($I$7,0),J$7&gt;EOMONTH($I$7,1))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -58182,6 +58126,34 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="22a266b9fa9a230c5a512669d8b298c3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="eddc33fff6b14141ee5c74a0d29ea6a1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -58457,35 +58429,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39060724-9CA2-4290-8A0C-B53624A594E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA4BA2A8-DB97-40F9-8DB6-154C09C7467C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75C87518-DD8E-42CD-8DAC-291A323E849B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -58504,24 +58468,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA4BA2A8-DB97-40F9-8DB6-154C09C7467C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39060724-9CA2-4290-8A0C-B53624A594E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/7_Allegati/Gantt.xlsx
+++ b/7_Allegati/Gantt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marco\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Scuola\Classe\I3AA\M306 - Progetti\game-project\7_Allegati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C846B49-8B58-4A0F-858F-28A8A39C0263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55011FC3-4EAA-4F6C-A16B-31F854236B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Leggero" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -126,9 +129,6 @@
   </si>
   <si>
     <t>Attività cardine</t>
-  </si>
-  <si>
-    <t>Gestione missioni</t>
   </si>
   <si>
     <t>Lukas</t>
@@ -234,6 +234,9 @@
   </si>
   <si>
     <t>ven 22/05</t>
+  </si>
+  <si>
+    <t>Gestione livelli</t>
   </si>
 </sst>
 </file>
@@ -437,7 +440,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -584,19 +587,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -605,7 +595,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -744,7 +734,22 @@
     <xf numFmtId="167" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="12" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -759,31 +764,26 @@
     <xf numFmtId="165" fontId="12" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Data" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
     <cellStyle name="zTestoNascosto" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
   </cellStyles>
-  <dxfs count="61">
+  <dxfs count="93">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -904,7 +904,131 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF70AD47"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="-0.249977111117893"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0">
@@ -920,6 +1044,136 @@
           <bgColor rgb="FF70AD47"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -1161,6 +1415,214 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="2" tint="-9.9978637043366805E-2"/>
         </patternFill>
       </fill>
@@ -1276,16 +1738,21 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
         <top/>
-        <bottom/>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1424,89 +1891,6 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
           <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
@@ -1536,6 +1920,13 @@
           <color theme="0" tint="-0.34998626667073579"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF70AD47"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -1821,59 +2212,58 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DO99"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" customWidth="1"/>
-    <col min="2" max="2" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" style="44" customWidth="1"/>
-    <col min="6" max="6" width="18.44140625" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" customWidth="1"/>
-    <col min="8" max="11" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" style="44" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" customWidth="1"/>
+    <col min="7" max="7" width="2.7109375" customWidth="1"/>
+    <col min="8" max="11" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="14" width="8" customWidth="1"/>
     <col min="15" max="23" width="8" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="27" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="28" max="39" width="8" bestFit="1" customWidth="1"/>
-    <col min="40" max="45" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="7.5546875" customWidth="1"/>
-    <col min="47" max="47" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="40" max="45" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="7.5703125" customWidth="1"/>
+    <col min="47" max="47" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="8" customWidth="1"/>
     <col min="50" max="51" width="8" bestFit="1" customWidth="1"/>
-    <col min="52" max="59" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="4.44140625" customWidth="1"/>
+    <col min="52" max="59" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="4.42578125" customWidth="1"/>
     <col min="61" max="61" width="3" customWidth="1"/>
-    <col min="62" max="66" width="2.6640625" customWidth="1"/>
+    <col min="62" max="66" width="2.7109375" customWidth="1"/>
     <col min="67" max="68" width="3" customWidth="1"/>
-    <col min="69" max="69" width="2.6640625" customWidth="1"/>
-    <col min="70" max="70" width="3.6640625" customWidth="1"/>
+    <col min="69" max="69" width="2.7109375" customWidth="1"/>
+    <col min="70" max="70" width="3.7109375" customWidth="1"/>
     <col min="71" max="71" width="13" customWidth="1"/>
-    <col min="72" max="90" width="3.6640625" customWidth="1"/>
-    <col min="91" max="91" width="2.6640625" customWidth="1"/>
-    <col min="92" max="92" width="16.5546875" customWidth="1"/>
-    <col min="93" max="94" width="2.6640625" customWidth="1"/>
+    <col min="72" max="90" width="3.7109375" customWidth="1"/>
+    <col min="91" max="91" width="2.7109375" customWidth="1"/>
+    <col min="92" max="92" width="16.5703125" customWidth="1"/>
+    <col min="93" max="94" width="2.7109375" customWidth="1"/>
     <col min="95" max="96" width="3" customWidth="1"/>
-    <col min="97" max="99" width="2.6640625" customWidth="1"/>
-    <col min="100" max="108" width="3.6640625" customWidth="1"/>
-    <col min="109" max="109" width="16.5546875" customWidth="1"/>
-    <col min="110" max="116" width="3.6640625" customWidth="1"/>
-    <col min="117" max="117" width="16.5546875" customWidth="1"/>
-    <col min="118" max="118" width="3.6640625" customWidth="1"/>
+    <col min="97" max="99" width="2.7109375" customWidth="1"/>
+    <col min="100" max="108" width="3.7109375" customWidth="1"/>
+    <col min="109" max="109" width="16.5703125" customWidth="1"/>
+    <col min="110" max="116" width="3.7109375" customWidth="1"/>
+    <col min="117" max="117" width="16.5703125" customWidth="1"/>
+    <col min="118" max="118" width="3.7109375" customWidth="1"/>
     <col min="119" max="119" width="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:119" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:119" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="53" t="s">
+    <row r="1" spans="1:119" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:119" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -1932,21 +2322,21 @@
       <c r="BK2" s="2"/>
       <c r="BL2" s="2"/>
     </row>
-    <row r="3" spans="1:119" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:119" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="4"/>
       <c r="E3" s="45"/>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
     </row>
-    <row r="4" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="7"/>
       <c r="E4" s="45"/>
     </row>
-    <row r="5" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="6"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -1954,7 +2344,7 @@
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
     </row>
-    <row r="6" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="8" t="s">
         <v>2</v>
       </c>
@@ -1965,52 +2355,52 @@
       <c r="E6" s="46"/>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="54" t="s">
+      <c r="H6" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="54"/>
-      <c r="M6" s="54"/>
-      <c r="N6" s="54"/>
-      <c r="O6" s="54"/>
-      <c r="P6" s="54"/>
-      <c r="Q6" s="54"/>
-      <c r="R6" s="54"/>
-      <c r="S6" s="54"/>
-      <c r="T6" s="54" t="s">
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="59"/>
+      <c r="N6" s="59"/>
+      <c r="O6" s="59"/>
+      <c r="P6" s="59"/>
+      <c r="Q6" s="59"/>
+      <c r="R6" s="59"/>
+      <c r="S6" s="59"/>
+      <c r="T6" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="U6" s="54"/>
-      <c r="V6" s="54"/>
-      <c r="W6" s="54"/>
-      <c r="X6" s="54"/>
-      <c r="Y6" s="54"/>
-      <c r="Z6" s="54"/>
-      <c r="AA6" s="54"/>
-      <c r="AB6" s="54"/>
-      <c r="AC6" s="54"/>
-      <c r="AD6" s="54"/>
-      <c r="AE6" s="54"/>
-      <c r="AF6" s="54"/>
-      <c r="AG6" s="54"/>
-      <c r="AH6" s="54"/>
-      <c r="AI6" s="54"/>
-      <c r="AJ6" s="54" t="s">
+      <c r="U6" s="59"/>
+      <c r="V6" s="59"/>
+      <c r="W6" s="59"/>
+      <c r="X6" s="59"/>
+      <c r="Y6" s="59"/>
+      <c r="Z6" s="59"/>
+      <c r="AA6" s="59"/>
+      <c r="AB6" s="59"/>
+      <c r="AC6" s="59"/>
+      <c r="AD6" s="59"/>
+      <c r="AE6" s="59"/>
+      <c r="AF6" s="59"/>
+      <c r="AG6" s="59"/>
+      <c r="AH6" s="59"/>
+      <c r="AI6" s="59"/>
+      <c r="AJ6" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="AK6" s="54"/>
-      <c r="AL6" s="54"/>
-      <c r="AM6" s="54"/>
-      <c r="AN6" s="54"/>
-      <c r="AO6" s="54"/>
-      <c r="AP6" s="54"/>
-      <c r="AQ6" s="54"/>
-      <c r="AR6" s="54"/>
-      <c r="AS6" s="54"/>
-      <c r="AT6" s="54"/>
-      <c r="AU6" s="54"/>
+      <c r="AK6" s="59"/>
+      <c r="AL6" s="59"/>
+      <c r="AM6" s="59"/>
+      <c r="AN6" s="59"/>
+      <c r="AO6" s="59"/>
+      <c r="AP6" s="59"/>
+      <c r="AQ6" s="59"/>
+      <c r="AR6" s="59"/>
+      <c r="AS6" s="59"/>
+      <c r="AT6" s="59"/>
+      <c r="AU6" s="59"/>
       <c r="AV6" s="12"/>
       <c r="AW6" s="13"/>
       <c r="AX6" s="13"/>
@@ -2084,7 +2474,7 @@
       <c r="DN6" s="12"/>
       <c r="DO6" s="12"/>
     </row>
-    <row r="7" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
@@ -2095,84 +2485,84 @@
       <c r="E7" s="47"/>
       <c r="F7" s="9"/>
       <c r="G7" s="17"/>
-      <c r="H7" s="55" t="s">
+      <c r="H7" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="55"/>
-      <c r="J7" s="55"/>
-      <c r="K7" s="55"/>
-      <c r="L7" s="52" t="s">
+      <c r="I7" s="60"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="60"/>
+      <c r="L7" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="52"/>
-      <c r="N7" s="52"/>
-      <c r="O7" s="52"/>
-      <c r="P7" s="52" t="s">
+      <c r="M7" s="56"/>
+      <c r="N7" s="56"/>
+      <c r="O7" s="56"/>
+      <c r="P7" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="Q7" s="52"/>
-      <c r="R7" s="52"/>
-      <c r="S7" s="52"/>
-      <c r="T7" s="52" t="s">
+      <c r="Q7" s="56"/>
+      <c r="R7" s="56"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="U7" s="52"/>
-      <c r="V7" s="52"/>
-      <c r="W7" s="52"/>
-      <c r="X7" s="52" t="s">
+      <c r="U7" s="56"/>
+      <c r="V7" s="56"/>
+      <c r="W7" s="56"/>
+      <c r="X7" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="Y7" s="52"/>
-      <c r="Z7" s="52"/>
-      <c r="AA7" s="52"/>
-      <c r="AB7" s="56" t="s">
+      <c r="Y7" s="56"/>
+      <c r="Z7" s="56"/>
+      <c r="AA7" s="56"/>
+      <c r="AB7" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="AC7" s="56"/>
-      <c r="AD7" s="56"/>
-      <c r="AE7" s="56"/>
-      <c r="AF7" s="56" t="s">
+      <c r="AC7" s="61"/>
+      <c r="AD7" s="61"/>
+      <c r="AE7" s="61"/>
+      <c r="AF7" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="AG7" s="56"/>
-      <c r="AH7" s="56"/>
-      <c r="AI7" s="56"/>
-      <c r="AJ7" s="52" t="s">
+      <c r="AG7" s="61"/>
+      <c r="AH7" s="61"/>
+      <c r="AI7" s="61"/>
+      <c r="AJ7" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="AK7" s="52"/>
-      <c r="AL7" s="52"/>
-      <c r="AM7" s="52"/>
-      <c r="AN7" s="52" t="s">
+      <c r="AK7" s="56"/>
+      <c r="AL7" s="56"/>
+      <c r="AM7" s="56"/>
+      <c r="AN7" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="AO7" s="52"/>
-      <c r="AP7" s="52"/>
-      <c r="AQ7" s="52"/>
-      <c r="AR7" s="52" t="s">
+      <c r="AO7" s="56"/>
+      <c r="AP7" s="56"/>
+      <c r="AQ7" s="56"/>
+      <c r="AR7" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="AS7" s="52"/>
-      <c r="AT7" s="52"/>
-      <c r="AU7" s="52"/>
-      <c r="AV7" s="52" t="s">
+      <c r="AS7" s="56"/>
+      <c r="AT7" s="56"/>
+      <c r="AU7" s="56"/>
+      <c r="AV7" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="AW7" s="56"/>
+      <c r="AX7" s="56"/>
+      <c r="AY7" s="56"/>
+      <c r="AZ7" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="AW7" s="52"/>
-      <c r="AX7" s="52"/>
-      <c r="AY7" s="52"/>
-      <c r="AZ7" s="52" t="s">
+      <c r="BA7" s="56"/>
+      <c r="BB7" s="56"/>
+      <c r="BC7" s="56"/>
+      <c r="BD7" s="56" t="s">
         <v>62</v>
       </c>
-      <c r="BA7" s="52"/>
-      <c r="BB7" s="52"/>
-      <c r="BC7" s="52"/>
-      <c r="BD7" s="52" t="s">
-        <v>63</v>
-      </c>
-      <c r="BE7" s="52"/>
-      <c r="BF7" s="52"/>
-      <c r="BG7" s="52"/>
+      <c r="BE7" s="56"/>
+      <c r="BF7" s="56"/>
+      <c r="BG7" s="56"/>
       <c r="BH7" s="18"/>
       <c r="BI7" s="18"/>
       <c r="BJ7" s="18"/>
@@ -2237,7 +2627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:119" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:119" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -2461,7 +2851,7 @@
       <c r="DN8" s="23"/>
       <c r="DO8" s="23"/>
     </row>
-    <row r="9" spans="1:119" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:119" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="24" t="s">
         <v>17</v>
       </c>
@@ -2698,7 +3088,7 @@
         <v>d</v>
       </c>
     </row>
-    <row r="10" spans="1:119" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:119" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="29"/>
       <c r="C10" s="30"/>
       <c r="D10" s="31"/>
@@ -2937,7 +3327,7 @@
       <c r="DN10" s="34"/>
       <c r="DO10" s="34"/>
     </row>
-    <row r="11" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="35"/>
       <c r="C11" s="36"/>
       <c r="D11" s="36"/>
@@ -3180,18 +3570,18 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="57" t="s">
+    <row r="12" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="40" t="s">
         <v>31</v>
-      </c>
-      <c r="B12" s="40" t="s">
-        <v>32</v>
       </c>
       <c r="C12" s="36" t="s">
         <v>26</v>
       </c>
       <c r="D12" s="36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E12" s="50">
         <v>46066</v>
@@ -3315,16 +3705,16 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="57"/>
+    <row r="13" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="53"/>
       <c r="B13" s="40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" s="36" t="s">
         <v>27</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E13" s="50">
         <v>46066</v>
@@ -3449,16 +3839,16 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="57"/>
+    <row r="14" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="53"/>
       <c r="B14" s="40" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" s="36" t="s">
         <v>26</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E14" s="50">
         <v>46073</v>
@@ -3583,16 +3973,16 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="57"/>
+    <row r="15" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="53"/>
       <c r="B15" s="40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" s="36" t="s">
         <v>26</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E15" s="50">
         <v>46073</v>
@@ -3717,16 +4107,16 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="57"/>
+    <row r="16" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="53"/>
       <c r="B16" s="40" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="36" t="s">
         <v>26</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E16" s="50">
         <v>46080</v>
@@ -3851,16 +4241,16 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="57"/>
+    <row r="17" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="53"/>
       <c r="B17" s="40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" s="36" t="s">
         <v>26</v>
       </c>
       <c r="D17" s="36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E17" s="50">
         <v>46087</v>
@@ -3882,13 +4272,13 @@
       <c r="R17" s="38"/>
       <c r="S17" s="38"/>
       <c r="T17" s="51" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="U17" s="51" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V17" s="51" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="W17" s="38"/>
       <c r="X17" s="38"/>
@@ -3991,16 +4381,16 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="58"/>
+    <row r="18" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="57"/>
       <c r="B18" s="40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" s="36" t="s">
         <v>26</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E18" s="50">
         <v>46087</v>
@@ -4024,7 +4414,7 @@
       <c r="T18" s="38"/>
       <c r="U18" s="38"/>
       <c r="V18" s="51" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="W18" s="51"/>
       <c r="X18" s="51"/>
@@ -4127,18 +4517,18 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="57" t="s">
+    <row r="19" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="40" t="s">
         <v>39</v>
-      </c>
-      <c r="B19" s="40" t="s">
-        <v>40</v>
       </c>
       <c r="C19" s="36" t="s">
         <v>26</v>
       </c>
       <c r="D19" s="36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E19" s="50">
         <v>46094</v>
@@ -4263,16 +4653,16 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="57"/>
+    <row r="20" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="53"/>
       <c r="B20" s="40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C20" s="36" t="s">
         <v>26</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E20" s="50">
         <v>46101</v>
@@ -4397,16 +4787,16 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="57"/>
+    <row r="21" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="53"/>
       <c r="B21" s="40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="36" t="s">
         <v>26</v>
       </c>
       <c r="D21" s="36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E21" s="50">
         <v>46101</v>
@@ -4531,23 +4921,23 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="58"/>
+    <row r="22" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="57"/>
       <c r="B22" s="40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" s="36" t="s">
         <v>26</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E22" s="50">
         <f t="shared" ref="E22:E34" si="1">E21+7</f>
         <v>46108</v>
       </c>
       <c r="F22" s="37">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G22" s="36"/>
       <c r="H22" s="38"/>
@@ -4666,18 +5056,18 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="59" t="s">
+    <row r="23" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="52" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="40" t="s">
         <v>44</v>
-      </c>
-      <c r="B23" s="40" t="s">
-        <v>45</v>
       </c>
       <c r="C23" s="36" t="s">
         <v>26</v>
       </c>
       <c r="D23" s="36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E23" s="50">
         <v>46108</v>
@@ -4802,14 +5192,14 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="57"/>
+    <row r="24" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="53"/>
       <c r="B24" s="40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C24" s="36"/>
       <c r="D24" s="36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E24" s="50">
         <v>46115</v>
@@ -4931,16 +5321,16 @@
       <c r="DN24" s="39"/>
       <c r="DO24" s="39"/>
     </row>
-    <row r="25" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="57"/>
+    <row r="25" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="53"/>
       <c r="B25" s="40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" s="36" t="s">
         <v>26</v>
       </c>
       <c r="D25" s="36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E25" s="50">
         <f>E23+7</f>
@@ -5066,16 +5456,16 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="57"/>
+    <row r="26" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="53"/>
       <c r="B26" s="40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C26" s="36" t="s">
         <v>26</v>
       </c>
       <c r="D26" s="36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E26" s="50">
         <f t="shared" si="1"/>
@@ -5201,16 +5591,16 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="57"/>
+    <row r="27" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="53"/>
       <c r="B27" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C27" s="36" t="s">
         <v>26</v>
       </c>
       <c r="D27" s="36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E27" s="50">
         <f t="shared" si="1"/>
@@ -5336,16 +5726,16 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="58"/>
+    <row r="28" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="57"/>
       <c r="B28" s="40" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="C28" s="36" t="s">
         <v>26</v>
       </c>
       <c r="D28" s="36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E28" s="50">
         <f t="shared" si="1"/>
@@ -5471,18 +5861,18 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="59" t="s">
+    <row r="29" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="40" t="s">
         <v>49</v>
-      </c>
-      <c r="B29" s="40" t="s">
-        <v>50</v>
       </c>
       <c r="C29" s="36" t="s">
         <v>26</v>
       </c>
       <c r="D29" s="36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E29" s="50">
         <f>E28+7</f>
@@ -5608,16 +5998,16 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="57"/>
+    <row r="30" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="53"/>
       <c r="B30" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C30" s="36" t="s">
         <v>26</v>
       </c>
       <c r="D30" s="36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E30" s="50">
         <f t="shared" si="1"/>
@@ -5743,16 +6133,16 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="57"/>
+    <row r="31" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="53"/>
       <c r="B31" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C31" s="36" t="s">
         <v>26</v>
       </c>
       <c r="D31" s="36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E31" s="50">
         <f t="shared" si="1"/>
@@ -5878,16 +6268,16 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="57"/>
+    <row r="32" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="53"/>
       <c r="B32" s="40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C32" s="36" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E32" s="50">
         <f t="shared" si="1"/>
@@ -6013,18 +6403,18 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="62" t="s">
+    <row r="33" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="40" t="s">
         <v>54</v>
-      </c>
-      <c r="B33" s="40" t="s">
-        <v>55</v>
       </c>
       <c r="C33" s="36" t="s">
         <v>26</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E33" s="50">
         <f>E32+7</f>
@@ -6081,9 +6471,10 @@
       <c r="AZ33" s="39"/>
       <c r="BA33" s="39"/>
       <c r="BB33" s="39"/>
-      <c r="BC33" s="39"/>
-      <c r="BE33" s="51"/>
-      <c r="BF33" s="51"/>
+      <c r="BC33" s="51"/>
+      <c r="BD33" s="51"/>
+      <c r="BE33" s="39"/>
+      <c r="BF33" s="39"/>
       <c r="BG33" s="39"/>
       <c r="BH33" s="39"/>
       <c r="BI33" s="39"/>
@@ -6149,16 +6540,16 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="60"/>
+    <row r="34" spans="1:119" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="55"/>
       <c r="B34" s="40" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C34" s="36" t="s">
         <v>26</v>
       </c>
       <c r="D34" s="36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E34" s="50">
         <f t="shared" si="1"/>
@@ -6217,8 +6608,8 @@
       <c r="BB34" s="39"/>
       <c r="BC34" s="39"/>
       <c r="BD34" s="39"/>
-      <c r="BE34" s="39"/>
-      <c r="BF34" s="39"/>
+      <c r="BE34" s="51"/>
+      <c r="BF34" s="51"/>
       <c r="BG34" s="39"/>
       <c r="BH34" s="39"/>
       <c r="BI34" s="39"/>
@@ -6284,8 +6675,8 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="61"/>
+    <row r="35" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="38"/>
       <c r="B35" s="38"/>
       <c r="C35" s="38"/>
       <c r="D35" s="38"/>
@@ -6408,7 +6799,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="38"/>
       <c r="B36" s="38"/>
       <c r="C36" s="38"/>
@@ -6532,7 +6923,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="38"/>
       <c r="B37" s="38"/>
       <c r="C37" s="38"/>
@@ -6656,7 +7047,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="38"/>
       <c r="B38" s="38"/>
       <c r="C38" s="38"/>
@@ -6780,7 +7171,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="39" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="38"/>
       <c r="B39" s="38"/>
       <c r="C39" s="38"/>
@@ -6904,7 +7295,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="40" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="38"/>
       <c r="B40" s="38"/>
       <c r="C40" s="38"/>
@@ -7028,7 +7419,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="38"/>
       <c r="B41" s="38"/>
       <c r="C41" s="38"/>
@@ -7152,7 +7543,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="38"/>
       <c r="B42" s="38"/>
       <c r="C42" s="38"/>
@@ -7276,7 +7667,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="38"/>
       <c r="B43" s="38"/>
       <c r="C43" s="38"/>
@@ -7400,7 +7791,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="38"/>
       <c r="B44" s="38"/>
       <c r="C44" s="38"/>
@@ -7524,7 +7915,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="38"/>
       <c r="B45" s="38"/>
       <c r="C45" s="38"/>
@@ -7648,7 +8039,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="38"/>
       <c r="B46" s="38"/>
       <c r="C46" s="38"/>
@@ -7772,7 +8163,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="38"/>
       <c r="B47" s="38"/>
       <c r="C47" s="38"/>
@@ -7896,7 +8287,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="38"/>
       <c r="B48" s="38"/>
       <c r="C48" s="38"/>
@@ -8020,7 +8411,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="38"/>
       <c r="B49" s="38"/>
       <c r="C49" s="38"/>
@@ -8144,7 +8535,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="38"/>
       <c r="B50" s="38"/>
       <c r="C50" s="38"/>
@@ -8268,7 +8659,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="38"/>
       <c r="B51" s="38"/>
       <c r="C51" s="38"/>
@@ -8392,7 +8783,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="38"/>
       <c r="B52" s="38"/>
       <c r="C52" s="38"/>
@@ -8516,7 +8907,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="38"/>
       <c r="B53" s="38"/>
       <c r="C53" s="38"/>
@@ -8640,7 +9031,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="38"/>
       <c r="B54" s="38"/>
       <c r="C54" s="38"/>
@@ -8764,7 +9155,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="38"/>
       <c r="B55" s="38"/>
       <c r="C55" s="38"/>
@@ -8888,7 +9279,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="38"/>
       <c r="B56" s="38"/>
       <c r="C56" s="38"/>
@@ -9012,7 +9403,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="38"/>
       <c r="B57" s="38"/>
       <c r="C57" s="38"/>
@@ -9136,7 +9527,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="38"/>
       <c r="B58" s="38"/>
       <c r="C58" s="38"/>
@@ -9260,7 +9651,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="38"/>
       <c r="B59" s="38"/>
       <c r="C59" s="38"/>
@@ -9384,7 +9775,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="38"/>
       <c r="B60" s="38"/>
       <c r="C60" s="38"/>
@@ -9508,7 +9899,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="38"/>
       <c r="B61" s="38"/>
       <c r="C61" s="38"/>
@@ -9632,7 +10023,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="38"/>
       <c r="B62" s="38"/>
       <c r="C62" s="38"/>
@@ -9756,7 +10147,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="38"/>
       <c r="B63" s="38"/>
       <c r="C63" s="38"/>
@@ -9880,7 +10271,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="38"/>
       <c r="B64" s="38"/>
       <c r="C64" s="38"/>
@@ -10004,7 +10395,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="38"/>
       <c r="B65" s="38"/>
       <c r="C65" s="38"/>
@@ -10128,7 +10519,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="38"/>
       <c r="B66" s="38"/>
       <c r="C66" s="38"/>
@@ -10252,7 +10643,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="38"/>
       <c r="B67" s="38"/>
       <c r="C67" s="38"/>
@@ -10376,7 +10767,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="38"/>
       <c r="B68" s="38"/>
       <c r="C68" s="38"/>
@@ -10500,7 +10891,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="38"/>
       <c r="B69" s="38"/>
       <c r="C69" s="38"/>
@@ -10624,7 +11015,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="38"/>
       <c r="B70" s="38"/>
       <c r="C70" s="38"/>
@@ -10748,7 +11139,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="38"/>
       <c r="B71" s="38"/>
       <c r="C71" s="38"/>
@@ -10872,7 +11263,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="38"/>
       <c r="B72" s="38"/>
       <c r="C72" s="38"/>
@@ -10996,7 +11387,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="38"/>
       <c r="B73" s="38"/>
       <c r="C73" s="38"/>
@@ -11120,7 +11511,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="38"/>
       <c r="B74" s="38"/>
       <c r="C74" s="38"/>
@@ -11244,7 +11635,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="38"/>
       <c r="B75" s="38"/>
       <c r="C75" s="38"/>
@@ -11368,7 +11759,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="38"/>
       <c r="B76" s="38"/>
       <c r="C76" s="38"/>
@@ -11492,7 +11883,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="38"/>
       <c r="B77" s="38"/>
       <c r="C77" s="38"/>
@@ -11616,7 +12007,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="38"/>
       <c r="B78" s="38"/>
       <c r="C78" s="38"/>
@@ -11740,7 +12131,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="38"/>
       <c r="B79" s="38"/>
       <c r="C79" s="38"/>
@@ -11864,7 +12255,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="38"/>
       <c r="B80" s="38"/>
       <c r="C80" s="38"/>
@@ -11988,7 +12379,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="38"/>
       <c r="B81" s="38"/>
       <c r="C81" s="38"/>
@@ -12112,7 +12503,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="38"/>
       <c r="B82" s="38"/>
       <c r="C82" s="38"/>
@@ -12236,7 +12627,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="38"/>
       <c r="B83" s="38"/>
       <c r="C83" s="38"/>
@@ -12360,7 +12751,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="38"/>
       <c r="B84" s="38"/>
       <c r="C84" s="38"/>
@@ -12484,7 +12875,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="38"/>
       <c r="B85" s="38"/>
       <c r="C85" s="38"/>
@@ -12608,7 +12999,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="38"/>
       <c r="B86" s="38"/>
       <c r="C86" s="38"/>
@@ -12732,7 +13123,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="38"/>
       <c r="B87" s="38"/>
       <c r="C87" s="38"/>
@@ -12856,7 +13247,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="38"/>
       <c r="B88" s="38"/>
       <c r="C88" s="38"/>
@@ -12980,7 +13371,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="38"/>
       <c r="B89" s="38"/>
       <c r="C89" s="38"/>
@@ -13104,7 +13495,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="38"/>
       <c r="B90" s="38"/>
       <c r="C90" s="38"/>
@@ -13228,7 +13619,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="38"/>
       <c r="B91" s="38"/>
       <c r="C91" s="38"/>
@@ -13349,7 +13740,7 @@
       <c r="DN91" s="39"/>
       <c r="DO91" s="39"/>
     </row>
-    <row r="92" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H92" s="42" t="str">
         <f>IF(AND(OR($C92="Obiettivo",$C92="Attività cardine"),$E92=H8,1&lt;=$F92),1,"")</f>
         <v/>
@@ -13511,7 +13902,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H93" s="42" t="str">
         <f>IF(AND(OR($C93="Obiettivo",$C93="Attività cardine"),$E93=H8,1&lt;=$F93),1,"")</f>
         <v/>
@@ -13673,7 +14064,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H94" s="42" t="str">
         <f>IF(AND(OR($C94="Obiettivo",$C94="Attività cardine"),$E94=H8,1&lt;=$F94),1,"")</f>
         <v/>
@@ -13835,7 +14226,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H95" s="42" t="str">
         <f>IF(AND(OR($C95="Obiettivo",$C95="Attività cardine"),$E95=H8,1&lt;=$F95),1,"")</f>
         <v/>
@@ -13997,7 +14388,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H96" s="42" t="str">
         <f>IF(AND(OR($C96="Obiettivo",$C96="Attività cardine"),$E96=H8,1&lt;=$F96),1,"")</f>
         <v/>
@@ -14159,7 +14550,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="2:47" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:47" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H97" s="42" t="str">
         <f>IF(AND(OR($C97="Obiettivo",$C97="Attività cardine"),$E97=H8,1&lt;=$F97),1,"")</f>
         <v/>
@@ -14321,7 +14712,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="2:47" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:47" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H98" s="42" t="str">
         <f>IF(AND(OR($C98="Obiettivo",$C98="Attività cardine"),$E98=H8,1&lt;=$F98),1,"")</f>
         <v/>
@@ -14483,7 +14874,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="2:47" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:47" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="43"/>
       <c r="H99" s="42" t="str">
         <f>IF(AND(OR($C99="Obiettivo",$C99="Attività cardine"),$E99=H8,1&lt;=$F99),1,"")</f>
@@ -14648,12 +15039,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A29:A32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="AR7:AU7"/>
-    <mergeCell ref="A12:A18"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A23:A28"/>
     <mergeCell ref="AV7:AY7"/>
     <mergeCell ref="AZ7:BC7"/>
     <mergeCell ref="BD7:BG7"/>
@@ -14670,234 +15055,345 @@
     <mergeCell ref="AF7:AI7"/>
     <mergeCell ref="AJ7:AM7"/>
     <mergeCell ref="AN7:AQ7"/>
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="AR7:AU7"/>
+    <mergeCell ref="A12:A18"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A23:A28"/>
   </mergeCells>
-  <conditionalFormatting sqref="H12:J12 H10:AU11 L12:AU12 H34:AU99 H13:AU22 H23:AS33">
-    <cfRule type="cellIs" dxfId="60" priority="276" operator="equal">
+  <conditionalFormatting sqref="A35:G91">
+    <cfRule type="cellIs" dxfId="92" priority="35" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12:J12 H13:AU22 H23:AS33 H10:AU11 L12:AU12 H34:AU99">
+    <cfRule type="cellIs" dxfId="91" priority="298" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:AL6 BL6:CP6 DD6:DO6">
-    <cfRule type="expression" dxfId="59" priority="269">
+    <cfRule type="expression" dxfId="90" priority="291">
       <formula>H$7&lt;=EOMONTH($H$7,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:DO6">
-    <cfRule type="expression" dxfId="58" priority="267">
+    <cfRule type="expression" dxfId="89" priority="289">
       <formula>AND(H$7&lt;=EOMONTH($H$7,1),H$7&gt;EOMONTH($H$7,0))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H10:DO11 H12:J13 L12:DO13 K13 P14:DO14 H14:AU16 H15:DO16 H17:S18 AA17:DO18 H19:DO22 H23:AF33 H34:BE34 BH23:DO33 BG34:DO34 H35:DO37 H40:DO91 A35:G91">
-    <cfRule type="expression" dxfId="57" priority="279">
+  <conditionalFormatting sqref="H10:DO11 H12:J13 L12:DO13 K13 P14:DO14 H14:AU16 H15:DO16 H17:S18 AA17:DO18 H19:DO22 H23:AF33 H34:BD34 H35:DO37 H40:DO91 BH23:DO33 BG34:DO34 A35:G91">
+    <cfRule type="expression" dxfId="88" priority="301">
       <formula>AND($C10="Rischio basso",A$7&gt;=$E10,A$7&lt;=$E10+$F10-1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H10:DO11 H12:J13 L12:DO13 K13 P14:DO14 H14:AU16 H15:DO16 H17:S18 AA17:DO18 H19:DO22 H23:AF33 BH23:DO33 H34:BE34 BG34:DO34 H35:DO37 H40:DO91 A35:G91">
-    <cfRule type="expression" dxfId="56" priority="280">
+  <conditionalFormatting sqref="H10:DO11 H12:J13 L12:DO13 K13 P14:DO14 H14:AU16 H15:DO16 H17:S18 AA17:DO18 H19:DO22 H23:AF33 BH23:DO33 H34:BD34 BG34:DO34 H35:DO37 H40:DO91 A35:G91">
+    <cfRule type="expression" dxfId="87" priority="302">
       <formula>AND($C10="Rischio alto",A$7&gt;=$E10,A$7&lt;=$E10+$F10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="281">
+    <cfRule type="expression" dxfId="86" priority="303">
       <formula>AND($C10="In linea",A$7&gt;=$E10,A$7&lt;=$E10+$F10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="282">
+    <cfRule type="expression" dxfId="85" priority="304">
       <formula>AND($C10="Rischio medio",A$7&gt;=$E10,A$7&lt;=$E10+$F10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="283">
+    <cfRule type="expression" dxfId="84" priority="305">
       <formula>AND(LEN($C10)=0,A$7&gt;=$E10,A$7&lt;=$E10+$F10-1)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H38:DO39">
+    <cfRule type="expression" dxfId="83" priority="408">
+      <formula>AND($C38="Rischio basso",H$7&gt;=#REF!,H$7&lt;=#REF!+$F38-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="82" priority="413">
+      <formula>AND($C38="Rischio alto",H$7&gt;=#REF!,H$7&lt;=#REF!+$F38-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="81" priority="414">
+      <formula>AND($C38="In linea",H$7&gt;=#REF!,H$7&lt;=#REF!+$F38-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="80" priority="415">
+      <formula>AND($C38="Rischio medio",H$7&gt;=#REF!,H$7&lt;=#REF!+$F38-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="79" priority="416">
+      <formula>AND(LEN($C38)=0,H$7&gt;=#REF!,H$7&lt;=#REF!+$F38-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I6:DO6">
-    <cfRule type="expression" dxfId="52" priority="268">
+    <cfRule type="expression" dxfId="78" priority="290">
       <formula>AND(I$7&lt;=EOMONTH($H$7,2),I$7&gt;EOMONTH($H$7,0),I$7&gt;EOMONTH($H$7,1))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J12 J14:N14 AG23:BE32 AG33:BC33 BE33:BF33">
-    <cfRule type="expression" dxfId="51" priority="256">
-      <formula>AND($C12="Rischio basso",L$7&gt;=$E12,L$7&lt;=$E12+$F12-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="50" priority="257">
+  <conditionalFormatting sqref="J12 J14:N14 AG23:BE32 AG33:BB33">
+    <cfRule type="expression" dxfId="77" priority="279">
       <formula>AND($C12="Rischio alto",L$7&gt;=$E12,L$7&lt;=$E12+$F12-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="258">
+    <cfRule type="expression" dxfId="76" priority="280">
       <formula>AND($C12="In linea",L$7&gt;=$E12,L$7&lt;=$E12+$F12-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="259">
+    <cfRule type="expression" dxfId="75" priority="281">
       <formula>AND($C12="Rischio medio",L$7&gt;=$E12,L$7&lt;=$E12+$F12-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="260">
+    <cfRule type="expression" dxfId="74" priority="282">
       <formula>AND(LEN($C12)=0,L$7&gt;=$E12,L$7&lt;=$E12+$F12-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="expression" dxfId="46" priority="292">
+    <cfRule type="expression" dxfId="73" priority="314">
       <formula>AND($C13="Rischio basso",M$7&gt;=$E13,M$7&lt;=$E13+$F13-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="293">
+    <cfRule type="expression" dxfId="72" priority="315">
       <formula>AND($C13="Rischio alto",M$7&gt;=$E13,M$7&lt;=$E13+$F13-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="294">
+    <cfRule type="expression" dxfId="71" priority="316">
       <formula>AND($C13="In linea",M$7&gt;=$E13,M$7&lt;=$E13+$F13-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="295">
+    <cfRule type="expression" dxfId="70" priority="317">
       <formula>AND($C13="Rischio medio",M$7&gt;=$E13,M$7&lt;=$E13+$F13-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="296">
+    <cfRule type="expression" dxfId="69" priority="318">
       <formula>AND(LEN($C13)=0,M$7&gt;=$E13,M$7&lt;=$E13+$F13-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T17:Z17 AA19:AB19 AC20:AD20 AE21">
-    <cfRule type="expression" dxfId="41" priority="305">
-      <formula>AND($C18="Rischio basso",T$7&gt;=$E18,T$7&lt;=$E18+$F18-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="40" priority="306">
+    <cfRule type="expression" dxfId="68" priority="328">
       <formula>AND($C18="Rischio alto",T$7&gt;=$E18,T$7&lt;=$E18+$F18-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="307">
+    <cfRule type="expression" dxfId="67" priority="329">
       <formula>AND($C18="In linea",T$7&gt;=$E18,T$7&lt;=$E18+$F18-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="308">
+    <cfRule type="expression" dxfId="66" priority="330">
       <formula>AND($C18="Rischio medio",T$7&gt;=$E18,T$7&lt;=$E18+$F18-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="309">
+    <cfRule type="expression" dxfId="65" priority="331">
       <formula>AND(LEN($C18)=0,T$7&gt;=$E18,T$7&lt;=$E18+$F18-1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BF23:BG32 BG33">
-    <cfRule type="expression" dxfId="36" priority="251">
-      <formula>AND($C23="Rischio basso",BF$7&gt;=$E23,BF$7&lt;=$E23+$F23-1)</formula>
+  <conditionalFormatting sqref="T18:Z18 AF22:AH22">
+    <cfRule type="expression" dxfId="64" priority="495">
+      <formula>AND(#REF!="Rischio alto",T$7&gt;=#REF!,T$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="252">
-      <formula>AND($C23="Rischio alto",BF$7&gt;=$E23,BF$7&lt;=$E23+$F23-1)</formula>
+    <cfRule type="expression" dxfId="63" priority="496">
+      <formula>AND(#REF!="In linea",T$7&gt;=#REF!,T$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="253">
-      <formula>AND($C23="In linea",BF$7&gt;=$E23,BF$7&lt;=$E23+$F23-1)</formula>
+    <cfRule type="expression" dxfId="62" priority="497">
+      <formula>AND(#REF!="Rischio medio",T$7&gt;=#REF!,T$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="254">
-      <formula>AND($C23="Rischio medio",BF$7&gt;=$E23,BF$7&lt;=$E23+$F23-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="255">
-      <formula>AND(LEN($C23)=0,BF$7&gt;=$E23,BF$7&lt;=$E23+$F23-1)</formula>
+    <cfRule type="expression" dxfId="61" priority="498">
+      <formula>AND(LEN(#REF!)=0,T$7&gt;=#REF!,T$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG23:AH23 AI24:AJ24 AK25 AL26:AQ26 AR27:AS27 AX29 AY30:AZ30 BA31 BE33:BF33">
-    <cfRule type="expression" dxfId="31" priority="362">
+  <conditionalFormatting sqref="AA19:AB19 AC20:AD20 AE21 T17:Z17">
+    <cfRule type="expression" dxfId="60" priority="327">
+      <formula>AND($C18="Rischio basso",T$7&gt;=$E18,T$7&lt;=$E18+$F18-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF22:AH22 T18:Z18">
+    <cfRule type="expression" dxfId="59" priority="494">
+      <formula>AND(#REF!="Rischio basso",T$7&gt;=#REF!,T$7&lt;=#REF!+#REF!-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG23:AH23 AI24:AJ24 AK25 AL26:AQ26 AR27:AS27 AX29 AY30:AZ30 BA31">
+    <cfRule type="expression" dxfId="58" priority="384">
       <formula>AND($C24="Rischio basso",AI$7&gt;=$E24,AI$7&lt;=$E24+$F24-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="363">
+    <cfRule type="expression" dxfId="57" priority="385">
       <formula>AND($C24="Rischio alto",AI$7&gt;=$E24,AI$7&lt;=$E24+$F24-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="364">
+    <cfRule type="expression" dxfId="56" priority="386">
       <formula>AND($C24="In linea",AI$7&gt;=$E24,AI$7&lt;=$E24+$F24-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="365">
+    <cfRule type="expression" dxfId="55" priority="387">
       <formula>AND($C24="Rischio medio",AI$7&gt;=$E24,AI$7&lt;=$E24+$F24-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="366">
+    <cfRule type="expression" dxfId="54" priority="388">
       <formula>AND(LEN($C24)=0,AI$7&gt;=$E24,AI$7&lt;=$E24+$F24-1)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AG23:BE32 J12 J14:N14 AG33:BB33">
+    <cfRule type="expression" dxfId="53" priority="278">
+      <formula>AND($C12="Rischio basso",L$7&gt;=$E12,L$7&lt;=$E12+$F12-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AT28:AW28 BB32">
+    <cfRule type="expression" dxfId="52" priority="581">
+      <formula>AND(#REF!="Rischio basso",AV$7&gt;=#REF!,AV$7&lt;=#REF!+#REF!-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="51" priority="582">
+      <formula>AND(#REF!="Rischio alto",AV$7&gt;=#REF!,AV$7&lt;=#REF!+#REF!-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="50" priority="583">
+      <formula>AND(#REF!="In linea",AV$7&gt;=#REF!,AV$7&lt;=#REF!+#REF!-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="49" priority="584">
+      <formula>AND(#REF!="Rischio medio",AV$7&gt;=#REF!,AV$7&lt;=#REF!+#REF!-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="48" priority="585">
+      <formula>AND(LEN(#REF!)=0,AV$7&gt;=#REF!,AV$7&lt;=#REF!+#REF!-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AT28:AW28">
-    <cfRule type="cellIs" dxfId="26" priority="126" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="148" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AX29">
-    <cfRule type="cellIs" dxfId="25" priority="120" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="142" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AY30:AZ30">
-    <cfRule type="cellIs" dxfId="24" priority="108" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="130" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA31">
-    <cfRule type="cellIs" dxfId="23" priority="102" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="124" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB32">
-    <cfRule type="cellIs" dxfId="22" priority="96" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="118" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BE33:BF33">
-    <cfRule type="cellIs" dxfId="21" priority="78" operator="equal">
+  <conditionalFormatting sqref="BC33:BD33">
+    <cfRule type="cellIs" dxfId="42" priority="100" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BF23:BG32 BE33:BG33">
+    <cfRule type="expression" dxfId="36" priority="273">
+      <formula>AND($C23="Rischio basso",BE$7&gt;=$E23,BE$7&lt;=$E23+$F23-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="35" priority="274">
+      <formula>AND($C23="Rischio alto",BE$7&gt;=$E23,BE$7&lt;=$E23+$F23-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="275">
+      <formula>AND($C23="In linea",BE$7&gt;=$E23,BE$7&lt;=$E23+$F23-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="276">
+      <formula>AND($C23="Rischio medio",BE$7&gt;=$E23,BE$7&lt;=$E23+$F23-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="277">
+      <formula>AND(LEN($C23)=0,BE$7&gt;=$E23,BE$7&lt;=$E23+$F23-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BC33:BD33">
+    <cfRule type="expression" dxfId="31" priority="620">
+      <formula>AND($C33="Rischio alto",BG$7&gt;=$E33,BG$7&lt;=$E33+$F33-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="621">
+      <formula>AND($C33="In linea",BG$7&gt;=$E33,BG$7&lt;=$E33+$F33-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="622">
+      <formula>AND($C33="Rischio medio",BG$7&gt;=$E33,BG$7&lt;=$E33+$F33-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="623">
+      <formula>AND(LEN($C33)=0,BG$7&gt;=$E33,BG$7&lt;=$E33+$F33-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BC33:BD33">
+    <cfRule type="expression" dxfId="27" priority="624">
+      <formula>AND($C34="Rischio basso",BG$7&gt;=$E34,BG$7&lt;=$E34+$F34-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="625">
+      <formula>AND($C34="Rischio alto",BG$7&gt;=$E34,BG$7&lt;=$E34+$F34-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="626">
+      <formula>AND($C34="In linea",BG$7&gt;=$E34,BG$7&lt;=$E34+$F34-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="627">
+      <formula>AND($C34="Rischio medio",BG$7&gt;=$E34,BG$7&lt;=$E34+$F34-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="628">
+      <formula>AND(LEN($C34)=0,BG$7&gt;=$E34,BG$7&lt;=$E34+$F34-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BC33:BD33">
+    <cfRule type="expression" dxfId="22" priority="629">
+      <formula>AND($C33="Rischio basso",BG$7&gt;=$E33,BG$7&lt;=$E33+$F33-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BE34">
+    <cfRule type="cellIs" dxfId="21" priority="12" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BE34">
+    <cfRule type="expression" dxfId="20" priority="13">
+      <formula>AND($C34="Rischio alto",BI$7&gt;=$E34,BI$7&lt;=$E34+$F34-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="14">
+      <formula>AND($C34="In linea",BI$7&gt;=$E34,BI$7&lt;=$E34+$F34-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="15">
+      <formula>AND($C34="Rischio medio",BI$7&gt;=$E34,BI$7&lt;=$E34+$F34-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="16">
+      <formula>AND(LEN($C34)=0,BI$7&gt;=$E34,BI$7&lt;=$E34+$F34-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BE34">
+    <cfRule type="expression" dxfId="16" priority="17">
+      <formula>AND($C35="Rischio basso",BI$7&gt;=$E35,BI$7&lt;=$E35+$F35-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="18">
+      <formula>AND($C35="Rischio alto",BI$7&gt;=$E35,BI$7&lt;=$E35+$F35-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="19">
+      <formula>AND($C35="In linea",BI$7&gt;=$E35,BI$7&lt;=$E35+$F35-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="20">
+      <formula>AND($C35="Rischio medio",BI$7&gt;=$E35,BI$7&lt;=$E35+$F35-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="21">
+      <formula>AND(LEN($C35)=0,BI$7&gt;=$E35,BI$7&lt;=$E35+$F35-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BE34">
+    <cfRule type="expression" dxfId="11" priority="22">
+      <formula>AND($C34="Rischio basso",BI$7&gt;=$E34,BI$7&lt;=$E34+$F34-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BF34">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF34">
-    <cfRule type="expression" dxfId="20" priority="315">
-      <formula>AND($C33="Rischio basso",BF$7&gt;=$E33,BF$7&lt;=$E33+$F33-1)</formula>
+    <cfRule type="expression" dxfId="9" priority="2">
+      <formula>AND($C34="Rischio alto",BJ$7&gt;=$E34,BJ$7&lt;=$E34+$F34-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="316">
-      <formula>AND($C33="Rischio alto",BF$7&gt;=$E33,BF$7&lt;=$E33+$F33-1)</formula>
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>AND($C34="In linea",BJ$7&gt;=$E34,BJ$7&lt;=$E34+$F34-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="317">
-      <formula>AND($C33="In linea",BF$7&gt;=$E33,BF$7&lt;=$E33+$F33-1)</formula>
+    <cfRule type="expression" dxfId="7" priority="4">
+      <formula>AND($C34="Rischio medio",BJ$7&gt;=$E34,BJ$7&lt;=$E34+$F34-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="318">
-      <formula>AND($C33="Rischio medio",BF$7&gt;=$E33,BF$7&lt;=$E33+$F33-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="319">
-      <formula>AND(LEN($C33)=0,BF$7&gt;=$E33,BF$7&lt;=$E33+$F33-1)</formula>
+    <cfRule type="expression" dxfId="6" priority="5">
+      <formula>AND(LEN($C34)=0,BJ$7&gt;=$E34,BJ$7&lt;=$E34+$F34-1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H38:DO39">
-    <cfRule type="expression" dxfId="15" priority="386">
-      <formula>AND($C38="Rischio basso",H$7&gt;=#REF!,H$7&lt;=#REF!+$F38-1)</formula>
+  <conditionalFormatting sqref="BF34">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>AND($C35="Rischio basso",BJ$7&gt;=$E35,BJ$7&lt;=$E35+$F35-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="7">
+      <formula>AND($C35="Rischio alto",BJ$7&gt;=$E35,BJ$7&lt;=$E35+$F35-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="8">
+      <formula>AND($C35="In linea",BJ$7&gt;=$E35,BJ$7&lt;=$E35+$F35-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="9">
+      <formula>AND($C35="Rischio medio",BJ$7&gt;=$E35,BJ$7&lt;=$E35+$F35-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="10">
+      <formula>AND(LEN($C35)=0,BJ$7&gt;=$E35,BJ$7&lt;=$E35+$F35-1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H38:DO39">
-    <cfRule type="expression" dxfId="14" priority="391">
-      <formula>AND($C38="Rischio alto",H$7&gt;=#REF!,H$7&lt;=#REF!+$F38-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="392">
-      <formula>AND($C38="In linea",H$7&gt;=#REF!,H$7&lt;=#REF!+$F38-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="393">
-      <formula>AND($C38="Rischio medio",H$7&gt;=#REF!,H$7&lt;=#REF!+$F38-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="394">
-      <formula>AND(LEN($C38)=0,H$7&gt;=#REF!,H$7&lt;=#REF!+$F38-1)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35:G91">
-    <cfRule type="cellIs" dxfId="10" priority="13" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T18:Z18 AF22:AH22">
-    <cfRule type="expression" dxfId="9" priority="472">
-      <formula>AND(#REF!="Rischio basso",T$7&gt;=#REF!,T$7&lt;=#REF!+#REF!-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="473">
-      <formula>AND(#REF!="Rischio alto",T$7&gt;=#REF!,T$7&lt;=#REF!+#REF!-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="474">
-      <formula>AND(#REF!="In linea",T$7&gt;=#REF!,T$7&lt;=#REF!+#REF!-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="475">
-      <formula>AND(#REF!="Rischio medio",T$7&gt;=#REF!,T$7&lt;=#REF!+#REF!-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="476">
-      <formula>AND(LEN(#REF!)=0,T$7&gt;=#REF!,T$7&lt;=#REF!+#REF!-1)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AT28:AW28 BB32">
-    <cfRule type="expression" dxfId="4" priority="559">
-      <formula>AND(#REF!="Rischio basso",AV$7&gt;=#REF!,AV$7&lt;=#REF!+#REF!-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="560">
-      <formula>AND(#REF!="Rischio alto",AV$7&gt;=#REF!,AV$7&lt;=#REF!+#REF!-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="561">
-      <formula>AND(#REF!="In linea",AV$7&gt;=#REF!,AV$7&lt;=#REF!+#REF!-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="562">
-      <formula>AND(#REF!="Rischio medio",AV$7&gt;=#REF!,AV$7&lt;=#REF!+#REF!-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="563">
-      <formula>AND(LEN(#REF!)=0,AV$7&gt;=#REF!,AV$7&lt;=#REF!+#REF!-1)</formula>
+  <conditionalFormatting sqref="BF34">
+    <cfRule type="expression" dxfId="0" priority="11">
+      <formula>AND($C34="Rischio basso",BJ$7&gt;=$E34,BJ$7&lt;=$E34+$F34-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="3">

--- a/7_Allegati/Gantt.xlsx
+++ b/7_Allegati/Gantt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Scuola\Classe\I3AA\M306 - Progetti\game-project\7_Allegati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55011FC3-4EAA-4F6C-A16B-31F854236B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44CDFB5-5AA0-46B8-9C45-8D622B19F6BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -734,22 +734,7 @@
     <xf numFmtId="167" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="12" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -764,13 +749,28 @@
     <xf numFmtId="165" fontId="12" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Data" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
     <cellStyle name="zTestoNascosto" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
   </cellStyles>
-  <dxfs count="93">
+  <dxfs count="77">
     <dxf>
       <fill>
         <patternFill>
@@ -783,6 +783,156 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF70AD47"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -826,6 +976,19 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="7" tint="-0.249977111117893"/>
         </patternFill>
       </fill>
@@ -839,20 +1002,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+          <bgColor theme="6"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0">
@@ -878,7 +1028,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6"/>
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0">
@@ -924,7 +1074,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+          <bgColor theme="6"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0">
@@ -938,351 +1088,6 @@
       <fill>
         <patternFill>
           <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF70AD47"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.249977111117893"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0">
@@ -1343,14 +1148,85 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF70AD47"/>
+          <bgColor theme="5"/>
         </patternFill>
       </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
           <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0">
@@ -1390,6 +1266,19 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0">
@@ -1480,7 +1369,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
+          <bgColor theme="7" tint="-0.249977111117893"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0">
@@ -1493,20 +1382,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
+          <bgColor theme="5"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0">
@@ -1520,6 +1396,19 @@
       <fill>
         <patternFill>
           <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0">
@@ -1572,97 +1461,6 @@
       <fill>
         <patternFill>
           <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.249977111117893"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0">
@@ -1758,7 +1556,33 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0">
@@ -1784,33 +1608,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0">
@@ -2214,25 +2012,25 @@
   <dimension ref="A1:DO99"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" customWidth="1"/>
-    <col min="2" max="2" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" style="44" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" style="44" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.7109375" customWidth="1"/>
-    <col min="8" max="11" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="8" customWidth="1"/>
-    <col min="15" max="23" width="8" bestFit="1" customWidth="1"/>
-    <col min="24" max="27" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="39" width="8" bestFit="1" customWidth="1"/>
-    <col min="40" max="45" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="7.5703125" customWidth="1"/>
-    <col min="47" max="47" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="8" customWidth="1"/>
-    <col min="50" max="51" width="8" bestFit="1" customWidth="1"/>
-    <col min="52" max="59" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="27" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="31" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="35" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="39" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="40" max="43" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="44" max="48" width="8" bestFit="1" customWidth="1"/>
+    <col min="49" max="51" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="52" max="59" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="60" max="60" width="4.42578125" customWidth="1"/>
     <col min="61" max="61" width="3" customWidth="1"/>
     <col min="62" max="66" width="2.7109375" customWidth="1"/>
@@ -2251,19 +2049,19 @@
     <col min="110" max="116" width="3.7109375" customWidth="1"/>
     <col min="117" max="117" width="16.5703125" customWidth="1"/>
     <col min="118" max="118" width="3.7109375" customWidth="1"/>
-    <col min="119" max="119" width="2" bestFit="1" customWidth="1"/>
+    <col min="119" max="119" width="5.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:119" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -2355,52 +2153,52 @@
       <c r="E6" s="46"/>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="59" t="s">
+      <c r="H6" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="59"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="59"/>
-      <c r="L6" s="59"/>
-      <c r="M6" s="59"/>
-      <c r="N6" s="59"/>
-      <c r="O6" s="59"/>
-      <c r="P6" s="59"/>
-      <c r="Q6" s="59"/>
-      <c r="R6" s="59"/>
-      <c r="S6" s="59"/>
-      <c r="T6" s="59" t="s">
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="54"/>
+      <c r="M6" s="54"/>
+      <c r="N6" s="54"/>
+      <c r="O6" s="54"/>
+      <c r="P6" s="54"/>
+      <c r="Q6" s="54"/>
+      <c r="R6" s="54"/>
+      <c r="S6" s="54"/>
+      <c r="T6" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="U6" s="59"/>
-      <c r="V6" s="59"/>
-      <c r="W6" s="59"/>
-      <c r="X6" s="59"/>
-      <c r="Y6" s="59"/>
-      <c r="Z6" s="59"/>
-      <c r="AA6" s="59"/>
-      <c r="AB6" s="59"/>
-      <c r="AC6" s="59"/>
-      <c r="AD6" s="59"/>
-      <c r="AE6" s="59"/>
-      <c r="AF6" s="59"/>
-      <c r="AG6" s="59"/>
-      <c r="AH6" s="59"/>
-      <c r="AI6" s="59"/>
-      <c r="AJ6" s="59" t="s">
+      <c r="U6" s="54"/>
+      <c r="V6" s="54"/>
+      <c r="W6" s="54"/>
+      <c r="X6" s="54"/>
+      <c r="Y6" s="54"/>
+      <c r="Z6" s="54"/>
+      <c r="AA6" s="54"/>
+      <c r="AB6" s="54"/>
+      <c r="AC6" s="54"/>
+      <c r="AD6" s="54"/>
+      <c r="AE6" s="54"/>
+      <c r="AF6" s="54"/>
+      <c r="AG6" s="54"/>
+      <c r="AH6" s="54"/>
+      <c r="AI6" s="54"/>
+      <c r="AJ6" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="AK6" s="59"/>
-      <c r="AL6" s="59"/>
-      <c r="AM6" s="59"/>
-      <c r="AN6" s="59"/>
-      <c r="AO6" s="59"/>
-      <c r="AP6" s="59"/>
-      <c r="AQ6" s="59"/>
-      <c r="AR6" s="59"/>
-      <c r="AS6" s="59"/>
-      <c r="AT6" s="59"/>
-      <c r="AU6" s="59"/>
+      <c r="AK6" s="54"/>
+      <c r="AL6" s="54"/>
+      <c r="AM6" s="54"/>
+      <c r="AN6" s="54"/>
+      <c r="AO6" s="54"/>
+      <c r="AP6" s="54"/>
+      <c r="AQ6" s="54"/>
+      <c r="AR6" s="54"/>
+      <c r="AS6" s="54"/>
+      <c r="AT6" s="54"/>
+      <c r="AU6" s="54"/>
       <c r="AV6" s="12"/>
       <c r="AW6" s="13"/>
       <c r="AX6" s="13"/>
@@ -2485,84 +2283,84 @@
       <c r="E7" s="47"/>
       <c r="F7" s="9"/>
       <c r="G7" s="17"/>
-      <c r="H7" s="60" t="s">
+      <c r="H7" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="60"/>
-      <c r="L7" s="56" t="s">
+      <c r="I7" s="55"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="56"/>
-      <c r="N7" s="56"/>
-      <c r="O7" s="56"/>
-      <c r="P7" s="56" t="s">
+      <c r="M7" s="52"/>
+      <c r="N7" s="52"/>
+      <c r="O7" s="52"/>
+      <c r="P7" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="Q7" s="56"/>
-      <c r="R7" s="56"/>
-      <c r="S7" s="56"/>
-      <c r="T7" s="56" t="s">
+      <c r="Q7" s="52"/>
+      <c r="R7" s="52"/>
+      <c r="S7" s="52"/>
+      <c r="T7" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="U7" s="56"/>
-      <c r="V7" s="56"/>
-      <c r="W7" s="56"/>
-      <c r="X7" s="56" t="s">
+      <c r="U7" s="52"/>
+      <c r="V7" s="52"/>
+      <c r="W7" s="52"/>
+      <c r="X7" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="Y7" s="56"/>
-      <c r="Z7" s="56"/>
-      <c r="AA7" s="56"/>
-      <c r="AB7" s="61" t="s">
+      <c r="Y7" s="52"/>
+      <c r="Z7" s="52"/>
+      <c r="AA7" s="52"/>
+      <c r="AB7" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="AC7" s="61"/>
-      <c r="AD7" s="61"/>
-      <c r="AE7" s="61"/>
-      <c r="AF7" s="61" t="s">
+      <c r="AC7" s="56"/>
+      <c r="AD7" s="56"/>
+      <c r="AE7" s="56"/>
+      <c r="AF7" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="AG7" s="61"/>
-      <c r="AH7" s="61"/>
-      <c r="AI7" s="61"/>
-      <c r="AJ7" s="56" t="s">
+      <c r="AG7" s="56"/>
+      <c r="AH7" s="56"/>
+      <c r="AI7" s="56"/>
+      <c r="AJ7" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="AK7" s="56"/>
-      <c r="AL7" s="56"/>
-      <c r="AM7" s="56"/>
-      <c r="AN7" s="56" t="s">
+      <c r="AK7" s="52"/>
+      <c r="AL7" s="52"/>
+      <c r="AM7" s="52"/>
+      <c r="AN7" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="AO7" s="56"/>
-      <c r="AP7" s="56"/>
-      <c r="AQ7" s="56"/>
-      <c r="AR7" s="56" t="s">
+      <c r="AO7" s="52"/>
+      <c r="AP7" s="52"/>
+      <c r="AQ7" s="52"/>
+      <c r="AR7" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="AS7" s="56"/>
-      <c r="AT7" s="56"/>
-      <c r="AU7" s="56"/>
-      <c r="AV7" s="56" t="s">
+      <c r="AS7" s="52"/>
+      <c r="AT7" s="52"/>
+      <c r="AU7" s="52"/>
+      <c r="AV7" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="AW7" s="56"/>
-      <c r="AX7" s="56"/>
-      <c r="AY7" s="56"/>
-      <c r="AZ7" s="56" t="s">
+      <c r="AW7" s="52"/>
+      <c r="AX7" s="52"/>
+      <c r="AY7" s="52"/>
+      <c r="AZ7" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="BA7" s="56"/>
-      <c r="BB7" s="56"/>
-      <c r="BC7" s="56"/>
-      <c r="BD7" s="56" t="s">
+      <c r="BA7" s="52"/>
+      <c r="BB7" s="52"/>
+      <c r="BC7" s="52"/>
+      <c r="BD7" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="BE7" s="56"/>
-      <c r="BF7" s="56"/>
-      <c r="BG7" s="56"/>
+      <c r="BE7" s="52"/>
+      <c r="BF7" s="52"/>
+      <c r="BG7" s="52"/>
       <c r="BH7" s="18"/>
       <c r="BI7" s="18"/>
       <c r="BJ7" s="18"/>
@@ -3571,7 +3369,7 @@
       </c>
     </row>
     <row r="12" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="58" t="s">
         <v>30</v>
       </c>
       <c r="B12" s="40" t="s">
@@ -3706,7 +3504,7 @@
       </c>
     </row>
     <row r="13" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="53"/>
+      <c r="A13" s="58"/>
       <c r="B13" s="40" t="s">
         <v>32</v>
       </c>
@@ -3840,7 +3638,7 @@
       </c>
     </row>
     <row r="14" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="53"/>
+      <c r="A14" s="58"/>
       <c r="B14" s="40" t="s">
         <v>33</v>
       </c>
@@ -3974,7 +3772,7 @@
       </c>
     </row>
     <row r="15" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="53"/>
+      <c r="A15" s="58"/>
       <c r="B15" s="40" t="s">
         <v>34</v>
       </c>
@@ -4108,7 +3906,7 @@
       </c>
     </row>
     <row r="16" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="53"/>
+      <c r="A16" s="58"/>
       <c r="B16" s="40" t="s">
         <v>35</v>
       </c>
@@ -4242,7 +4040,7 @@
       </c>
     </row>
     <row r="17" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="53"/>
+      <c r="A17" s="58"/>
       <c r="B17" s="40" t="s">
         <v>36</v>
       </c>
@@ -4382,7 +4180,7 @@
       </c>
     </row>
     <row r="18" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="57"/>
+      <c r="A18" s="61"/>
       <c r="B18" s="40" t="s">
         <v>37</v>
       </c>
@@ -4518,7 +4316,7 @@
       </c>
     </row>
     <row r="19" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="53" t="s">
+      <c r="A19" s="58" t="s">
         <v>38</v>
       </c>
       <c r="B19" s="40" t="s">
@@ -4654,7 +4452,7 @@
       </c>
     </row>
     <row r="20" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="53"/>
+      <c r="A20" s="58"/>
       <c r="B20" s="40" t="s">
         <v>40</v>
       </c>
@@ -4788,7 +4586,7 @@
       </c>
     </row>
     <row r="21" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="53"/>
+      <c r="A21" s="58"/>
       <c r="B21" s="40" t="s">
         <v>41</v>
       </c>
@@ -4922,7 +4720,7 @@
       </c>
     </row>
     <row r="22" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="57"/>
+      <c r="A22" s="61"/>
       <c r="B22" s="40" t="s">
         <v>42</v>
       </c>
@@ -5057,7 +4855,7 @@
       </c>
     </row>
     <row r="23" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="52" t="s">
+      <c r="A23" s="57" t="s">
         <v>43</v>
       </c>
       <c r="B23" s="40" t="s">
@@ -5193,7 +4991,7 @@
       </c>
     </row>
     <row r="24" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="53"/>
+      <c r="A24" s="58"/>
       <c r="B24" s="40" t="s">
         <v>59</v>
       </c>
@@ -5322,7 +5120,7 @@
       <c r="DO24" s="39"/>
     </row>
     <row r="25" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="53"/>
+      <c r="A25" s="58"/>
       <c r="B25" s="40" t="s">
         <v>45</v>
       </c>
@@ -5457,7 +5255,7 @@
       </c>
     </row>
     <row r="26" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="53"/>
+      <c r="A26" s="58"/>
       <c r="B26" s="40" t="s">
         <v>46</v>
       </c>
@@ -5592,7 +5390,7 @@
       </c>
     </row>
     <row r="27" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="53"/>
+      <c r="A27" s="58"/>
       <c r="B27" s="40" t="s">
         <v>47</v>
       </c>
@@ -5727,7 +5525,7 @@
       </c>
     </row>
     <row r="28" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="57"/>
+      <c r="A28" s="61"/>
       <c r="B28" s="40" t="s">
         <v>63</v>
       </c>
@@ -5862,7 +5660,7 @@
       </c>
     </row>
     <row r="29" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="52" t="s">
+      <c r="A29" s="57" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="40" t="s">
@@ -5999,7 +5797,7 @@
       </c>
     </row>
     <row r="30" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="53"/>
+      <c r="A30" s="58"/>
       <c r="B30" s="40" t="s">
         <v>50</v>
       </c>
@@ -6134,7 +5932,7 @@
       </c>
     </row>
     <row r="31" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="53"/>
+      <c r="A31" s="58"/>
       <c r="B31" s="40" t="s">
         <v>51</v>
       </c>
@@ -6269,7 +6067,7 @@
       </c>
     </row>
     <row r="32" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="53"/>
+      <c r="A32" s="58"/>
       <c r="B32" s="40" t="s">
         <v>52</v>
       </c>
@@ -6404,7 +6202,7 @@
       </c>
     </row>
     <row r="33" spans="1:119" s="5" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="54" t="s">
+      <c r="A33" s="59" t="s">
         <v>53</v>
       </c>
       <c r="B33" s="40" t="s">
@@ -6541,7 +6339,7 @@
       </c>
     </row>
     <row r="34" spans="1:119" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="55"/>
+      <c r="A34" s="60"/>
       <c r="B34" s="40" t="s">
         <v>55</v>
       </c>
@@ -15039,6 +14837,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="AR7:AU7"/>
+    <mergeCell ref="A12:A18"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A23:A28"/>
     <mergeCell ref="AV7:AY7"/>
     <mergeCell ref="AZ7:BC7"/>
     <mergeCell ref="BD7:BG7"/>
@@ -15055,345 +14859,286 @@
     <mergeCell ref="AF7:AI7"/>
     <mergeCell ref="AJ7:AM7"/>
     <mergeCell ref="AN7:AQ7"/>
-    <mergeCell ref="A29:A32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="AR7:AU7"/>
-    <mergeCell ref="A12:A18"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A23:A28"/>
   </mergeCells>
   <conditionalFormatting sqref="A35:G91">
-    <cfRule type="cellIs" dxfId="92" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="35" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12:J12 H13:AU22 H23:AS33 H10:AU11 L12:AU12 H34:AU99">
-    <cfRule type="cellIs" dxfId="91" priority="298" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="298" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:AL6 BL6:CP6 DD6:DO6">
-    <cfRule type="expression" dxfId="90" priority="291">
+    <cfRule type="expression" dxfId="74" priority="291">
       <formula>H$7&lt;=EOMONTH($H$7,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:DO6">
-    <cfRule type="expression" dxfId="89" priority="289">
+    <cfRule type="expression" dxfId="73" priority="289">
       <formula>AND(H$7&lt;=EOMONTH($H$7,1),H$7&gt;EOMONTH($H$7,0))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H10:DO11 H12:J13 L12:DO13 K13 P14:DO14 H14:AU16 H15:DO16 H17:S18 AA17:DO18 H19:DO22 H23:AF33 H34:BD34 H35:DO37 H40:DO91 BH23:DO33 BG34:DO34 A35:G91">
-    <cfRule type="expression" dxfId="88" priority="301">
+  <conditionalFormatting sqref="H10:DO11 H12:J13 L12:DO13 K13 P14:DO14 H14:AU16 H15:DO16 H17:S18 AA17:DO18 H19:DO22 H23:AF33 H34:BD34 H35:DO37 H40:DO91 A35:G91 BH23:DO33 BG34:DO34">
+    <cfRule type="expression" dxfId="72" priority="301">
       <formula>AND($C10="Rischio basso",A$7&gt;=$E10,A$7&lt;=$E10+$F10-1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H10:DO11 H12:J13 L12:DO13 K13 P14:DO14 H14:AU16 H15:DO16 H17:S18 AA17:DO18 H19:DO22 H23:AF33 BH23:DO33 H34:BD34 BG34:DO34 H35:DO37 H40:DO91 A35:G91">
-    <cfRule type="expression" dxfId="87" priority="302">
+  <conditionalFormatting sqref="H10:DO11 H12:J13 L12:DO13 K13 P14:DO14 H14:AU16 H15:DO16 H17:S18 AA17:DO18 H19:DO22 H23:AF33 BH23:DO33 H34:BD34 BG34:DO34 H35:DO37 A35:G91 H40:DO91">
+    <cfRule type="expression" dxfId="71" priority="302">
       <formula>AND($C10="Rischio alto",A$7&gt;=$E10,A$7&lt;=$E10+$F10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="303">
+    <cfRule type="expression" dxfId="70" priority="303">
       <formula>AND($C10="In linea",A$7&gt;=$E10,A$7&lt;=$E10+$F10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="304">
+    <cfRule type="expression" dxfId="69" priority="304">
       <formula>AND($C10="Rischio medio",A$7&gt;=$E10,A$7&lt;=$E10+$F10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="305">
+    <cfRule type="expression" dxfId="68" priority="305">
       <formula>AND(LEN($C10)=0,A$7&gt;=$E10,A$7&lt;=$E10+$F10-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38:DO39">
-    <cfRule type="expression" dxfId="83" priority="408">
-      <formula>AND($C38="Rischio basso",H$7&gt;=#REF!,H$7&lt;=#REF!+$F38-1)</formula>
+    <cfRule type="expression" dxfId="67" priority="416">
+      <formula>AND(LEN($C38)=0,H$7&gt;=#REF!,H$7&lt;=#REF!+$F38-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="413">
+    <cfRule type="expression" dxfId="66" priority="415">
+      <formula>AND($C38="Rischio medio",H$7&gt;=#REF!,H$7&lt;=#REF!+$F38-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="414">
+      <formula>AND($C38="In linea",H$7&gt;=#REF!,H$7&lt;=#REF!+$F38-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="413">
       <formula>AND($C38="Rischio alto",H$7&gt;=#REF!,H$7&lt;=#REF!+$F38-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="414">
-      <formula>AND($C38="In linea",H$7&gt;=#REF!,H$7&lt;=#REF!+$F38-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="80" priority="415">
-      <formula>AND($C38="Rischio medio",H$7&gt;=#REF!,H$7&lt;=#REF!+$F38-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="79" priority="416">
-      <formula>AND(LEN($C38)=0,H$7&gt;=#REF!,H$7&lt;=#REF!+$F38-1)</formula>
+    <cfRule type="expression" dxfId="63" priority="408">
+      <formula>AND($C38="Rischio basso",H$7&gt;=#REF!,H$7&lt;=#REF!+$F38-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:DO6">
-    <cfRule type="expression" dxfId="78" priority="290">
+    <cfRule type="expression" dxfId="62" priority="290">
       <formula>AND(I$7&lt;=EOMONTH($H$7,2),I$7&gt;EOMONTH($H$7,0),I$7&gt;EOMONTH($H$7,1))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12 J14:N14 AG23:BE32 AG33:BB33">
-    <cfRule type="expression" dxfId="77" priority="279">
+    <cfRule type="expression" dxfId="61" priority="279">
       <formula>AND($C12="Rischio alto",L$7&gt;=$E12,L$7&lt;=$E12+$F12-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="280">
+    <cfRule type="expression" dxfId="60" priority="280">
       <formula>AND($C12="In linea",L$7&gt;=$E12,L$7&lt;=$E12+$F12-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="75" priority="281">
+    <cfRule type="expression" dxfId="59" priority="281">
       <formula>AND($C12="Rischio medio",L$7&gt;=$E12,L$7&lt;=$E12+$F12-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="282">
+    <cfRule type="expression" dxfId="58" priority="282">
       <formula>AND(LEN($C12)=0,L$7&gt;=$E12,L$7&lt;=$E12+$F12-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="expression" dxfId="73" priority="314">
+    <cfRule type="expression" dxfId="57" priority="314">
       <formula>AND($C13="Rischio basso",M$7&gt;=$E13,M$7&lt;=$E13+$F13-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="315">
+    <cfRule type="expression" dxfId="56" priority="318">
+      <formula>AND(LEN($C13)=0,M$7&gt;=$E13,M$7&lt;=$E13+$F13-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="55" priority="315">
       <formula>AND($C13="Rischio alto",M$7&gt;=$E13,M$7&lt;=$E13+$F13-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="71" priority="316">
+    <cfRule type="expression" dxfId="54" priority="316">
       <formula>AND($C13="In linea",M$7&gt;=$E13,M$7&lt;=$E13+$F13-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="317">
+    <cfRule type="expression" dxfId="53" priority="317">
       <formula>AND($C13="Rischio medio",M$7&gt;=$E13,M$7&lt;=$E13+$F13-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="69" priority="318">
-      <formula>AND(LEN($C13)=0,M$7&gt;=$E13,M$7&lt;=$E13+$F13-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T17:Z17 AA19:AB19 AC20:AD20 AE21">
-    <cfRule type="expression" dxfId="68" priority="328">
-      <formula>AND($C18="Rischio alto",T$7&gt;=$E18,T$7&lt;=$E18+$F18-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="67" priority="329">
+    <cfRule type="expression" dxfId="52" priority="329">
       <formula>AND($C18="In linea",T$7&gt;=$E18,T$7&lt;=$E18+$F18-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="330">
+    <cfRule type="expression" dxfId="51" priority="331">
+      <formula>AND(LEN($C18)=0,T$7&gt;=$E18,T$7&lt;=$E18+$F18-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="50" priority="330">
       <formula>AND($C18="Rischio medio",T$7&gt;=$E18,T$7&lt;=$E18+$F18-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="331">
-      <formula>AND(LEN($C18)=0,T$7&gt;=$E18,T$7&lt;=$E18+$F18-1)</formula>
+    <cfRule type="expression" dxfId="49" priority="328">
+      <formula>AND($C18="Rischio alto",T$7&gt;=$E18,T$7&lt;=$E18+$F18-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T18:Z18 AF22:AH22">
-    <cfRule type="expression" dxfId="64" priority="495">
+    <cfRule type="expression" dxfId="48" priority="495">
       <formula>AND(#REF!="Rischio alto",T$7&gt;=#REF!,T$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="496">
+    <cfRule type="expression" dxfId="47" priority="496">
       <formula>AND(#REF!="In linea",T$7&gt;=#REF!,T$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="497">
+    <cfRule type="expression" dxfId="46" priority="497">
       <formula>AND(#REF!="Rischio medio",T$7&gt;=#REF!,T$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="498">
+    <cfRule type="expression" dxfId="45" priority="498">
       <formula>AND(LEN(#REF!)=0,T$7&gt;=#REF!,T$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA19:AB19 AC20:AD20 AE21 T17:Z17">
-    <cfRule type="expression" dxfId="60" priority="327">
+    <cfRule type="expression" dxfId="44" priority="327">
       <formula>AND($C18="Rischio basso",T$7&gt;=$E18,T$7&lt;=$E18+$F18-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF22:AH22 T18:Z18">
-    <cfRule type="expression" dxfId="59" priority="494">
+    <cfRule type="expression" dxfId="43" priority="494">
       <formula>AND(#REF!="Rischio basso",T$7&gt;=#REF!,T$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG23:AH23 AI24:AJ24 AK25 AL26:AQ26 AR27:AS27 AX29 AY30:AZ30 BA31">
-    <cfRule type="expression" dxfId="58" priority="384">
-      <formula>AND($C24="Rischio basso",AI$7&gt;=$E24,AI$7&lt;=$E24+$F24-1)</formula>
+    <cfRule type="expression" dxfId="42" priority="388">
+      <formula>AND(LEN($C24)=0,AI$7&gt;=$E24,AI$7&lt;=$E24+$F24-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="385">
+    <cfRule type="expression" dxfId="41" priority="385">
       <formula>AND($C24="Rischio alto",AI$7&gt;=$E24,AI$7&lt;=$E24+$F24-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="386">
+    <cfRule type="expression" dxfId="40" priority="386">
       <formula>AND($C24="In linea",AI$7&gt;=$E24,AI$7&lt;=$E24+$F24-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="387">
+    <cfRule type="expression" dxfId="39" priority="387">
       <formula>AND($C24="Rischio medio",AI$7&gt;=$E24,AI$7&lt;=$E24+$F24-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="388">
-      <formula>AND(LEN($C24)=0,AI$7&gt;=$E24,AI$7&lt;=$E24+$F24-1)</formula>
+    <cfRule type="expression" dxfId="38" priority="384">
+      <formula>AND($C24="Rischio basso",AI$7&gt;=$E24,AI$7&lt;=$E24+$F24-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG23:BE32 J12 J14:N14 AG33:BB33">
-    <cfRule type="expression" dxfId="53" priority="278">
+    <cfRule type="expression" dxfId="37" priority="278">
       <formula>AND($C12="Rischio basso",L$7&gt;=$E12,L$7&lt;=$E12+$F12-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT28:AW28 BB32">
-    <cfRule type="expression" dxfId="52" priority="581">
+    <cfRule type="expression" dxfId="36" priority="581">
       <formula>AND(#REF!="Rischio basso",AV$7&gt;=#REF!,AV$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="582">
+    <cfRule type="expression" dxfId="35" priority="582">
       <formula>AND(#REF!="Rischio alto",AV$7&gt;=#REF!,AV$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="583">
+    <cfRule type="expression" dxfId="34" priority="583">
       <formula>AND(#REF!="In linea",AV$7&gt;=#REF!,AV$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="584">
+    <cfRule type="expression" dxfId="33" priority="585">
+      <formula>AND(LEN(#REF!)=0,AV$7&gt;=#REF!,AV$7&lt;=#REF!+#REF!-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="584">
       <formula>AND(#REF!="Rischio medio",AV$7&gt;=#REF!,AV$7&lt;=#REF!+#REF!-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="585">
-      <formula>AND(LEN(#REF!)=0,AV$7&gt;=#REF!,AV$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT28:AW28">
-    <cfRule type="cellIs" dxfId="47" priority="148" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="148" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AX29">
-    <cfRule type="cellIs" dxfId="46" priority="142" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="142" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AY30:AZ30">
-    <cfRule type="cellIs" dxfId="45" priority="130" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="130" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA31">
-    <cfRule type="cellIs" dxfId="44" priority="124" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="124" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB32">
-    <cfRule type="cellIs" dxfId="43" priority="118" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="118" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BC33:BD33">
-    <cfRule type="cellIs" dxfId="42" priority="100" operator="equal">
+    <cfRule type="expression" dxfId="26" priority="624">
+      <formula>AND($C34="Rischio basso",BG$7&gt;=$E34,BG$7&lt;=$E34+$F34-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="622">
+      <formula>AND($C33="Rischio medio",BG$7&gt;=$E33,BG$7&lt;=$E33+$F33-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="621">
+      <formula>AND($C33="In linea",BG$7&gt;=$E33,BG$7&lt;=$E33+$F33-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="629">
+      <formula>AND($C33="Rischio basso",BG$7&gt;=$E33,BG$7&lt;=$E33+$F33-1)</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="100" operator="equal">
       <formula>1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="620">
+      <formula>AND($C33="Rischio alto",BG$7&gt;=$E33,BG$7&lt;=$E33+$F33-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="628">
+      <formula>AND(LEN($C34)=0,BG$7&gt;=$E34,BG$7&lt;=$E34+$F34-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="627">
+      <formula>AND($C34="Rischio medio",BG$7&gt;=$E34,BG$7&lt;=$E34+$F34-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="626">
+      <formula>AND($C34="In linea",BG$7&gt;=$E34,BG$7&lt;=$E34+$F34-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="625">
+      <formula>AND($C34="Rischio alto",BG$7&gt;=$E34,BG$7&lt;=$E34+$F34-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="623">
+      <formula>AND(LEN($C33)=0,BG$7&gt;=$E33,BG$7&lt;=$E33+$F33-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BE34:BF34">
+    <cfRule type="expression" dxfId="15" priority="3">
+      <formula>AND($C34="In linea",BI$7&gt;=$E34,BI$7&lt;=$E34+$F34-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="4">
+      <formula>AND($C34="Rischio medio",BI$7&gt;=$E34,BI$7&lt;=$E34+$F34-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="5">
+      <formula>AND(LEN($C34)=0,BI$7&gt;=$E34,BI$7&lt;=$E34+$F34-1)</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="7">
+      <formula>AND($C35="Rischio alto",BI$7&gt;=$E35,BI$7&lt;=$E35+$F35-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>AND($C34="Rischio alto",BI$7&gt;=$E34,BI$7&lt;=$E34+$F34-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="11">
+      <formula>AND($C34="Rischio basso",BI$7&gt;=$E34,BI$7&lt;=$E34+$F34-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="10">
+      <formula>AND(LEN($C35)=0,BI$7&gt;=$E35,BI$7&lt;=$E35+$F35-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="9">
+      <formula>AND($C35="Rischio medio",BI$7&gt;=$E35,BI$7&lt;=$E35+$F35-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="8">
+      <formula>AND($C35="In linea",BI$7&gt;=$E35,BI$7&lt;=$E35+$F35-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>AND($C35="Rischio basso",BI$7&gt;=$E35,BI$7&lt;=$E35+$F35-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF23:BG32 BE33:BG33">
-    <cfRule type="expression" dxfId="36" priority="273">
-      <formula>AND($C23="Rischio basso",BE$7&gt;=$E23,BE$7&lt;=$E23+$F23-1)</formula>
+    <cfRule type="expression" dxfId="4" priority="277">
+      <formula>AND(LEN($C23)=0,BE$7&gt;=$E23,BE$7&lt;=$E23+$F23-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="274">
+    <cfRule type="expression" dxfId="3" priority="276">
+      <formula>AND($C23="Rischio medio",BE$7&gt;=$E23,BE$7&lt;=$E23+$F23-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="275">
+      <formula>AND($C23="In linea",BE$7&gt;=$E23,BE$7&lt;=$E23+$F23-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="274">
       <formula>AND($C23="Rischio alto",BE$7&gt;=$E23,BE$7&lt;=$E23+$F23-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="275">
-      <formula>AND($C23="In linea",BE$7&gt;=$E23,BE$7&lt;=$E23+$F23-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="276">
-      <formula>AND($C23="Rischio medio",BE$7&gt;=$E23,BE$7&lt;=$E23+$F23-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="277">
-      <formula>AND(LEN($C23)=0,BE$7&gt;=$E23,BE$7&lt;=$E23+$F23-1)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BC33:BD33">
-    <cfRule type="expression" dxfId="31" priority="620">
-      <formula>AND($C33="Rischio alto",BG$7&gt;=$E33,BG$7&lt;=$E33+$F33-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="621">
-      <formula>AND($C33="In linea",BG$7&gt;=$E33,BG$7&lt;=$E33+$F33-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="29" priority="622">
-      <formula>AND($C33="Rischio medio",BG$7&gt;=$E33,BG$7&lt;=$E33+$F33-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="623">
-      <formula>AND(LEN($C33)=0,BG$7&gt;=$E33,BG$7&lt;=$E33+$F33-1)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BC33:BD33">
-    <cfRule type="expression" dxfId="27" priority="624">
-      <formula>AND($C34="Rischio basso",BG$7&gt;=$E34,BG$7&lt;=$E34+$F34-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="625">
-      <formula>AND($C34="Rischio alto",BG$7&gt;=$E34,BG$7&lt;=$E34+$F34-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="25" priority="626">
-      <formula>AND($C34="In linea",BG$7&gt;=$E34,BG$7&lt;=$E34+$F34-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="627">
-      <formula>AND($C34="Rischio medio",BG$7&gt;=$E34,BG$7&lt;=$E34+$F34-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="23" priority="628">
-      <formula>AND(LEN($C34)=0,BG$7&gt;=$E34,BG$7&lt;=$E34+$F34-1)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BC33:BD33">
-    <cfRule type="expression" dxfId="22" priority="629">
-      <formula>AND($C33="Rischio basso",BG$7&gt;=$E33,BG$7&lt;=$E33+$F33-1)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BE34">
-    <cfRule type="cellIs" dxfId="21" priority="12" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BE34">
-    <cfRule type="expression" dxfId="20" priority="13">
-      <formula>AND($C34="Rischio alto",BI$7&gt;=$E34,BI$7&lt;=$E34+$F34-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="19" priority="14">
-      <formula>AND($C34="In linea",BI$7&gt;=$E34,BI$7&lt;=$E34+$F34-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="15">
-      <formula>AND($C34="Rischio medio",BI$7&gt;=$E34,BI$7&lt;=$E34+$F34-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="17" priority="16">
-      <formula>AND(LEN($C34)=0,BI$7&gt;=$E34,BI$7&lt;=$E34+$F34-1)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BE34">
-    <cfRule type="expression" dxfId="16" priority="17">
-      <formula>AND($C35="Rischio basso",BI$7&gt;=$E35,BI$7&lt;=$E35+$F35-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="18">
-      <formula>AND($C35="Rischio alto",BI$7&gt;=$E35,BI$7&lt;=$E35+$F35-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="19">
-      <formula>AND($C35="In linea",BI$7&gt;=$E35,BI$7&lt;=$E35+$F35-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="20">
-      <formula>AND($C35="Rischio medio",BI$7&gt;=$E35,BI$7&lt;=$E35+$F35-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="21">
-      <formula>AND(LEN($C35)=0,BI$7&gt;=$E35,BI$7&lt;=$E35+$F35-1)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BE34">
-    <cfRule type="expression" dxfId="11" priority="22">
-      <formula>AND($C34="Rischio basso",BI$7&gt;=$E34,BI$7&lt;=$E34+$F34-1)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BF34">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BF34">
-    <cfRule type="expression" dxfId="9" priority="2">
-      <formula>AND($C34="Rischio alto",BJ$7&gt;=$E34,BJ$7&lt;=$E34+$F34-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="3">
-      <formula>AND($C34="In linea",BJ$7&gt;=$E34,BJ$7&lt;=$E34+$F34-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="4">
-      <formula>AND($C34="Rischio medio",BJ$7&gt;=$E34,BJ$7&lt;=$E34+$F34-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="5">
-      <formula>AND(LEN($C34)=0,BJ$7&gt;=$E34,BJ$7&lt;=$E34+$F34-1)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BF34">
-    <cfRule type="expression" dxfId="5" priority="6">
-      <formula>AND($C35="Rischio basso",BJ$7&gt;=$E35,BJ$7&lt;=$E35+$F35-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="7">
-      <formula>AND($C35="Rischio alto",BJ$7&gt;=$E35,BJ$7&lt;=$E35+$F35-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="8">
-      <formula>AND($C35="In linea",BJ$7&gt;=$E35,BJ$7&lt;=$E35+$F35-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="9">
-      <formula>AND($C35="Rischio medio",BJ$7&gt;=$E35,BJ$7&lt;=$E35+$F35-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="10">
-      <formula>AND(LEN($C35)=0,BJ$7&gt;=$E35,BJ$7&lt;=$E35+$F35-1)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BF34">
-    <cfRule type="expression" dxfId="0" priority="11">
-      <formula>AND($C34="Rischio basso",BJ$7&gt;=$E34,BJ$7&lt;=$E34+$F34-1)</formula>
+    <cfRule type="expression" dxfId="0" priority="273">
+      <formula>AND($C23="Rischio basso",BE$7&gt;=$E23,BE$7&lt;=$E23+$F23-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="3">
